--- a/battlebots_2015_2025.xlsx
+++ b/battlebots_2015_2025.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 10 (2020)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 11 (2021)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 12 (2022)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Features" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19887,4 +19888,6238 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Robot</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Wheel_Count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Extra_Reboot Seasons</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Extra_Other Events</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Extra_Other Names</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Team_Name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Extra_Team Members</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Extra_From</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Extra_Weapons</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Extra_Associated Robots</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Extra_Power</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Extra_Live</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Extra_Other Entries</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Extra_Comedy Central Seasons</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Extra_Unaired Events</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Extra_BotsIQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aegis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>World Championship V</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aegis  2.0 Zombie Aegis (BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Phalanx Robotics</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Chris Sparzo (Captain) Danielle Rossillo Andrew Godfrey Colin Stevens Alex Judge Timothy Homan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fishers, IN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Flipper</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Axe Backwards</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Team Axe Backwards (formerly KurTrox Robotix)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Kurt Durjan (Captain) Grant Pitcher Abra Durjan (WC III-WC IV) Garrett Durjan (WC III-WC IV) Hector Marini (WC III) Kevin Read (WC III) Taiowa Donovan (WC III) Dominic Read (WC III) John Stephens (WC IV-WC V) Tyler Phillips (WC IV-WC V) Tyler Monastero (WC IV) Matt Stephens (WC V) Bryce Barbato (WC V) Thomas Daede (WC V)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Vero Beach, FL</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full body drum spinner</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axolotl</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>235lbs</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Akimbo (working name)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Uh-Oh Robotics</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Alon Belkin (Captain) Leo Riesenbach Sele Okojie Victoria Tomozei Ishaan Gupta Jonathan Jones Jake Futterman Jack Collins Cooper Wahl</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Northridge, CA</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Gigabyte , Cobalt , Calypso , Banshee (Alon Belkin) Terrortops , DOOM (Victoria Tomozei) Glitch (Ishaan Gupta) Horizon (Alon Belkin, Victoria Tomozei) Tempest (Cooper Wahl)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6x MaxAmps 3S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bale Spear</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>227lbs (WC III) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship V</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Forge &amp; Farm Combat Robots</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Earl Pancoast III (Captain) Matt Bradway Kenny Blades (WC III) Joe Filigno (WC III) Kyle Singer (WC III) Alex Grant (WC III) Miro Matheson (WC V) Malcolm Matheson (WC V)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Salem, NJ</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pneumatic spear Punching fist (WC III)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Blacksmith (Kyle Singer, Earl Pancoast III) Red Devil (Earl Pancoast III) Animosity (Alex Grant) The Executioner , Roadkill (Miro Matheson)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Banshee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4x Flipsky 6384 brushless motors</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>World Championship VII</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions II BattleBots Pro League (2026) (Alternate)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Team Small Robots</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>David Small (Captain) Gus Collier Kevin Lillie Caleb Hecht Genny Korn Anne Lillie (BB Proving Ground) David Rush (BB Proving Ground) Jeff Waters (BB Proving Ground, BB Pro League 2026) Alon Belkin (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Pneumatic flipper</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Malice (David Small, David Rush) Pardon My French , Nelly the Ellybot (Gus Collier) Widowmaker (Kevin Lillie) JackPot (Jeff Waters) Gigabyte , Cobalt , Calypso , Axolotl (Alon Belkin)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2x Ovonic 16S 2200mAh LiPo battery packs</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023) BattleBots Proving Ground (2024) BattleBots FaceOffs (2025)</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Basilisk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>245lbs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MBS Robotics</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Lucas Sloan (Captain) Andrew Maier (WC II) David Sloan (WC II) Graham Jordan (WC II) Pierre Blanchard (WC III) Emily Ahlf (WC III)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Edmonton, Canada</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Flipper Pneumatic spike (WC II) Flamethrower (WC III)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Battle Royale With Cheese</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2x Electric scooter motors</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>World Championship III</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bacon Double Slamburger (Working name)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Team Poor Life Choices</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Miles Pekala (Captain) Jen Herchenroeder Jordan Bunker Lindsay Oliver Jim Burke Charles Wittington Brice Farrell Jeremy Ashinghurst Angela Rothbaum</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Oakland, CA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Skorpios , HiJinx (Jen Herchenroeder) Mammoth , Doomba (Brice Farrell)</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Gloomweaver , Fowl Play</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BattleSaw</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>World Championship II (Not selected) World Championship III (Withdrew) World Championship IV World Championship V (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Twister Robotics</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Adam Cox (Captain) Seth Cox (Captain) Jason Cox Chris Humble Mark Elam Curtis Nemeth Jeremiah Loder (WC II)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Wichita, KS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ring spinner</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Gamma 9 , Namreko 3000 , Gammatron , Gammacide (Curtis Nemeth) Bellator , Swamp Thing (Mark Elam)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2x Maytech 6880 brushless motors (WC VII-Present) 2x 48v Bosch DC motors (WC I-BB: Bounty Hunters) 2x 36V Magmotor S28-200 motors (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>250lbs (WC I-Present) 219lbs (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>World Championship I (Withdrew) World Championship II World Championship V World Championship VI (Withdrew) World Championship VII</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BETA βeta beta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Team Hurtz (formerly Team Robo Challenge )</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>John Reid (Captain) Dominic Parkinson (Season 5.0) George Francis (Season 5.0) Dave Moulds (WC I) Grant Cooper (WC II) Gabriel Stroud (WC V) Alan Cannon (WC V) Jason Marston (WC VII-Present) Andy Hibberd (WC VII-Present) Iona Parkinson (Comedy Central) Miranda Parkinson (Comedy Central) Gillie Blood (Comedy Central) Iona Foster (Comedy Central) Robert Kennett (Comedy Central)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Oxfordshire, UK</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cobalt , Gigabyte (Dave Moulds) Quantum (Grant Cooper) Sabretooth (Alan Cannon, Gabriel Stroud) DUCK! (Gabriel Stroud)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>12S LiPo batteries 3Ah NiCad BattlePacks (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>KillerHurtz , TerrorHurtz</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Season 5.0 (Withdrew)</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Big Dill</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4x Maytech 6374 brushless motors</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VII</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>The Big Dill</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Team Food Fight</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Emmanuel Carrillo (Captain) Isaak Malers (WC V) Brandon Young (WC V) Elizabeth Cao (WC V) Tommy Wong (WC V) Trent Wilson (BB: Champions I-Present) Ryan Lau (BB: Champions I) Ellis Ware (WC VII-Present) Andy Russell (WC VII-Present) Russ Barrow (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Lifting forks Flamethrower (BB: Champions I-Present) Vertical spinner (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>WAR Hawk , Jäger (Emmanuel Carrillo, Andy Russell) Overhaul (Elizabeth Cao) Horizon (Tommy Wong) MadCatter (Emmanuel Carrillo, Ryan Lau) Malice (Isaak Malers) Chronos (Trent Wilson) Dark Steel , Dark Shredder , Dome of Darkness (Russ Barrow) Goblin (Ellis Ware)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Bite Force</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2x S28-400 Magmotors (9hp) [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chompy (Working name) Biteforce</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Aptyx Designs</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Paul Ventimiglia (Captain) Teena Liu Cory McBride Jeremiah Jinno Travis Coving Anthony Ventimiglia (WC I) Colin Wilson (WC II) Rob Masek (WC III-WC IV) Tim Bogdanof (WC IV)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Grappler (WC I) Vertical bar spinner (WC II-re:MARS 2019)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>HiJinx (Tim Bogdanof) Lucky , Defender , Scrap Metal , FrostBite (Rob Masek)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>10x 5Ah 6S Turnigy Nano-tech LiPo batteries (WC II-WC III) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Brutality , Green Wave , Tantrum , Ntertainment , Land Shark , Knockturnal</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Black Dragon</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2x 8025 Brushless motors (WCVIII-Present) 2x Magmotors (WC IV-BB: Champions II)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Team Uai!rrior</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Julio Cortez (Captain) (WC VII-Present) João Marcos (WC IV-BB: Champions I) Guilherme Estreano dos Santos (WC IV) Gabriel Bertozzi (WC IV, WC VII-Present) Bruno Felipe Guimarães Silveira (WC IV) Felipe Duarte (WC IV &amp; WC VI-BB: Champions I) Gabriel Silveira Teles (WC V) Mateus Cintra (WC V-Present) Tarcísio Rezende (WC V-BB: Champions I) Murilo Sanchez de Oliveira (WC V) Gabriel Gomes (WC V-BB: Champions I) Moisés Araujo de Moura (WC V-BB: Champions I) Luis Gustavo Rufino de Souza (WC V) Nicholas Santana (WC VI-BB: Champions I) Vinicius Malaquias (WC VI-BB: Champions I) Tomás Costa (WC VII-Present) Amanda Batista (WC VII-Present) Alexandre Castilho (WC VII-Present) Vinicius Ferreira (WC VII-Present) Henrique Oliveira (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Itajubá, Brazil</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Eggbeater drum spinner Flamethrower</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>World Championship V</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Team Black Widow</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Herrick Henzel (Captain) Sue Henzel Braeton Henzel Jarrett Henzel Kyle Henzel</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Newport, NY</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Drum spinner Flamethrower</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship VI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Team Half Fast Astronaut</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Al Kindle (Captain) Alan Young John Wolan Sam Harrington (WC II) James Iocca (WC IV, VI-BB: Champions I) Kyle Singer (WC VI-BB: Champions I) Earl Pancoast III (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Edison, NJ</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Flamethrower hammer (WC II-WC IV) "Power hammer" (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Bale Spear (Earl Pancoast III, Kyle Singer) Golem , Scuttle (James Iocca)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Blip</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Moonshot (Working name)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Seems Reasonable Robotics</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Aren Hill (Captain) Bryan Culver Katie Widen Erica Chin James Doherty Zach Marks Will Stanley Steven Silverman Alex Grant Ginger Schmidt Dillon Carey David Mintz Brian Silverman Jason Weihman Alec Kochis Max Chang Sean Doherty Sue Doherty Kristine Atiyeh</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Flywheel flipper</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Insult and Injury (Aren Hill, Jason Weihman, Bryan Culver)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Tantrum , The Twins</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bloodsport</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4x Brushless TP Motors</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>247-250lbs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>BLOODSPORT</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bots 'n' Stuff Robotics</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Justin Marple (Captain) Aaron Lucas Nik Buchholz Jordan Kiesel Rebecca Miles (WC IV) Griffin Tabor (WC IV) Seth Schaffer (WC V-Present) Jordan Kiesel Matt Marple (WC V-Present) Rosa Ruiz (WC VI-Present) Claus Buchholz (WC VI) Katie Mumford (WC VI) Owen Marshall (WC VI-Present) Angel Marple (WC VI-Present) Brian Boxell (WC VII-Present) Riko Balakit (WC VII-Present) Michael Amoun (WC VII-Present) Omkar Powar (WC VII-Present) Curtis Honeycutt (WC VII-Present) Ellie Clark (WC VII-Present) Robert Lyle (WC VII-Present) Linden Siegall (BB Pro League 2026) Gillian DooLittle (BB Pro League 2026) Julia Marple (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Horizontal spinner</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>End Game (Griffin Tabor)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>10.8Ah 8S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023) BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Retrograde , Subatomic , Fireball</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bombshell</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4x Magmotors</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>245-250lbs</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Chaos Corps</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Randy Farmer (Captain) Mike Jeffries (WC II-WC III) Julie Simancek (WC II-WC III) Dan Hammer Matthew Carroll Jason Brown Chris Williamson (WC II-WC III) Brandon Davis (WC II-WC III) Jamie Price (WC II-WC III) Simon Arthur (WC II)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Vertical spinner (WC II-WC IV) Horizontal spinner (WC II-WC IV) Axe (WC II) Lifting forks (WC II)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Slammo! (Mike Jeffries, Randy Farmer, Jason Brown) Overhaul (Matthew Carroll) Edge (Chris Williamson) Interstellar Overdrive (Mike Jeffries, Julie Simancek) The Little Engine That Killed (Jamie Price) Neptune , Death Ray (Simon Arthur) Sublime (Chris Williamson)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>8s 10Ah LiPo battery</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Breaker Box</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4x Magmotors</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>140lbs (Cisco Party 2006) 220lbs (2009, WC IV)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>World Championship IV</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Cisco Party 2006</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Team Nightmare</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jim Smentowski (Captain) Clay Steere</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Bradenton, FL</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Lifting scoop Hammer (WC IV)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Rhino , Junior , Nightmare , Backlash , Whirligig , Turtle , ShazBot , MicroNightmare , Wallop , Grasshopper , The Swarm ( Locust )</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Pro Championship 2009</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bronco</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6x 3" Brushed motors (WC II) 4x motors (WC I, WC III-Present)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Destruct-A-Thon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Inertia Labs</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Alexander Rose (Captain) Reason Bradley (Captain) Christopher Daniel Nolan Van Dine (WC I-WC II) Matteo Borri (WC I-WC II) Greg Staples (WC I-WC II, WC IV) Brad Sykes (WC I-WC II) Scoutt Balchowsky (WC III-WC IV) Trey (WC IV) Mike (WC IV) Deonte Finch (Destruct-A-Thon) Eve Gray (Destruct-A-Thon) Sire Prince (Destruct-A-Thon) Lina Esteves (Destruct-A-Thon}</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sausalito, CA</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Flipping arm</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>LiFePO batteries (Destruct-A-Thon)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Toro , The Matador , T-Minus , Rhino , The Butcher</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brutus</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2x Brushless motors (WC III) 2x NPC brushed motors (WC II)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>242lbs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Team Brutus</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Adam Bercu (Captain) Andrew Berkowitz (WC II) Esther Shang (WC II) Joel Greenwood (WC II) Amanda Fowler (WC III) Luis Rosende (WC III) Ben Striegal (WC III)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Somerville, MA</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Vertical disk spinner Vertical bar spinner (WC III)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Overhaul , Witch Doctor , Coincidence (Adam Bercu) Valkyrie , RIPperoni , Starchild (Amanda Fowler)</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Captain Shrederator</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>220lbs [ 1 ]</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Shrederator Captain Shred. Cpt. Shred</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Team LOGICOM</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Brian Nave (Captain) (WC I-WC II, WC IV-Present) Nick Nave (WC III-Present) Mike Nave (WC I-WC III) Jacob Rogers (WC IV) Carmen Fucci (WC I-WC II) Joe Johnson (WC II-WC III) Ken Bryant (WC I-WC II, WC V) Brian Hauch (WC III-Present) Jonathan LaPlain (WC IV-Present) Geno Esposito (WC VI-BB: Champions I) Christopher Nave (WC VI-Present) Bradley Hanstad (WC III) Kim Wrenne (WC I) Zac O'Donnell (WC I) Scott Johnston (WC VII-Present) Caleb Finken (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ormond Beach, FL</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Shell spinner</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Lucky (Zac O'Donnell) Raven , Ultimo Destructo , Purple Fire (Jacob Rogers) Skorpios , Malice (Jonathan LaPlain) Triton , Deep Six , Bad Kitty , Switchback , Chronos , VD6.0 (Bradley Hanstad)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Chopper , Code:BLACK , Dispose-All , Phrizbee , Phrizbee-Ultimate , Shredhead , Pincer</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chomp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>250lbs (WC I-re:MARS 2019) 500lbs (WC V-BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship V</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The Machine Corps</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Zoe Stephenson (Captain) Jascha Little Jo Balme (WC II-WC III, WC V-BB: Bounty Hunters) Travis Smith (WC I) Scott Little (WC I) Aaron Cooper (WC I-WC II) Dimitar Vassilev (WC II) Randy Maniccia (WC V-BB: Bounty Hunters) Rachel Mark (WC V-BB: Bounty Hunters) Evan Finkle (WC V-BB: Bounty Hunters) Ellen Lackermann (WC V-BB: Bounty Hunters) Rusty Oliver (WC V-BB: Bounty Hunters) Matt Scott (WC V-BB: Bounty Hunters) Carina Wine (WC V-BB: Bounty Hunters) Neal Chapman (WC V-BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Flamethrower Crusher (WC I) Pneumatic hammer (WC II-re:MARS 2019) Turret hammer (WC V-BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>The Judge , The Prosecutor , Juggernaut (Jascha Little)</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chronos</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>243lbs</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Team Chronos</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Jerry Serafin (Captain) Johnny Melgoza Bradley Hanstad (WC IV) Nathan Trowbridge Nadia Moss Trent Wilson (WC V) Liana Bandžiulytė (WC V) Jennifer (WC VII)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Gardena, CA</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ring spinner</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Skorpios , Gigabyte , Bit Schlapp (Jerry Serafin) Triton , Deep Six , Captain Shrederator , VD6.0 , Switchback (Bradley Hanstad) Valkyrie , Horizon , Calypso (Kyle Loyola) Big Dill (Trent Wilson)</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No Luv , El Cucuy</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Claw Viper</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4x RV-120E brushless motors</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>250lbs ~238lbs (WC V) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026) (Withdrew)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Claw-Viper</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Team Bad Ideas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Kevin Milczewski (Captain) Brian Adamson (WC V-BB: Champions I) Dan Bostian Joshua Beavers Mike Thompson (WC VI-Present) Lindsay Pour (WC VII-Present) Alex Curtis (BB Proving Ground-Present)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Lifter Grappler</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>WAR Hawk (Kevin Milczewski, Joshua Beavers)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2x HyperDrive motors</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship IV World Championship V (Withdrew) World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Robotic Death Company (WC VI-Present) Team Carbide (WC II, WC IV)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Matt Olson (Captain) (BB FaceOffs-Present) John Mladenik (WC VI-Present) Dave Moulds (WC II, WC IV, WC VII-BB: Champions II) Sam Smith (WC II, WC IV, WC VII-BB: Champions II) Sheryl Prior (WC II) James Cooper (WC II) Danni Coxon (WC II) Andrew Kenworthy (WC IV) Mike Lindberg (WC VI-Present) Brent Rieker (WC VI-BB: Champions I) Matt Maxham (WC VI) Wendy Maxham (WC VI) Thy Phi (WC VI-Present) Elizabeth Mladenik (WC VI-Present) Melissa Mladenik (WC VI-Present) David Janssen (WC VI-Present) Anouk Janssen (WC VI-Present) Josh Hicok (WC VI) Carol Williams (WC VI-Present) Micah "Chewy" Leibowitz (WC VI-Present) Alon Belkin (WC VI) Conor O'Brien (WC VI) Jerry Serafin (WC VI) Derek Tran (WC VI-Present) Camden Wallraff (WC VI-BB: Champions II) Blair Lindberg (WC VI-Present) Cal Coker (WC VII-Present) Jesse Ramos (WC VII-Present) Adam Stewart (WC VII-Present) Lacy Stewart (WC VII-Present) Eric Fisher (WC VII-Present) Sri Ram Nervati (WC VII-Present) Michael Parks (BB Proving Ground) Royce Chung (BB FaceOffs 2024) Frank Zhao (BB FaceOffs 2024) Rohan Person (BB FaceOffs) David Le (BB FaceOffs) Mark Demers (BB Pro League 2026) Brandon Upshaw (BB Pro League 2026) Dane King (BB Pro League 2026) Megan Olson (BB Pro League 2026) Jason Boulanger (BB Pro League 2026) Jake Megarvey (BB Pro League 2026) Mike Duncan (BB Pro League 2026) Tammy Upshaw (BB Pro League 2026) Kayla Hope (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Oceanside, CA (previously Bromsgrove, UK)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Horizontal spinner (WC II) Vertical spinner (WC IV-Present)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Axolotl , Horizon (Alon Belkin) Wrecks , Skorpios , Tiki Fire (Micah Leibowitz) Stinger: The Killer Bee , Devil's Plunger , Sewer Snake , Wipe Out #2 (Matt Maxham, Wendy Maxham) Quantum (James Cooper) Beta (Dave Moulds) Taco Tuesday (Camden Wallraff) Lucky (Matt Olson, Mark Demers) Calypso (Alon Belkin, Derek Tran, Alex Price) Manta , Golden Fury (Derek Tran) JackPot (Derek Tran, David Le) Banshee (Alon Belkin, Alex Price) Nemesis (David Le) Ziggy , CycloneBot , PitBot , BravePart (Mark Demers)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Gigabyte , Megabyte , Rambite , Invader , Super Megabyte , Agsma</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Copperhead</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2x Maytech MTO6365 motors (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Night Crawler (Working name)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Team Copperhead (formerly Caustic Creations )</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Kyle Kirkpatrick (Captain) (BB Pro League 2026) James Kirkpatrick (BB Pro League 2026) Matt Starr (BB Pro League 2026) Ben Starr (BB Pro League 2026) Ryan Ly (BB Pro League 2026) Karl Neumann (BB Pro League 2026) Connor Bray (BB Pro League 2026) DJ Heiberger (BB Pro League 2026) Michael Joseph (BB Pro League 2026) Finn Joseph (BB Pro League 2026) Ryan Sturdivant (BB Pro League 2026) Nat Crawford (BB Pro League 2026) Jenna Starr (BB Pro League 2026) Daniel Heiberger (BB Pro League 2026) Karl Neumann (BB Pro League 2026) Luke Quintal (WC IV-WC VII) Zach Goff (WC IV-WC VII) Casey Kuhns (WC IV) Robert Cowan (WC IV-WC VI) Pete Covert (WC IV) Kimberley Cowan (WC IV-WC VI) Chad New (WC IV-WC VII) Micah Spinelli (WC IV-WC VII) Brad Henkel (WC IV-WC VII) Chris DeCicco (WC VII) Lindsay Baer (WC VII) Jonathan Clark (WC VII) Alec Mallinger (WC VII-Present) Maxwell New (WC VII) Heather Williams (WC VII)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Eggbeater drum spinner</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Chopper (Zach Goff) Magnitude (Chad New, Chris DeCicco, Alec Mallinger, Micah Spinelli, Kyle Kirkpatrick, James Kirkpatrick) Bling Bling (Chad New) MoZar (Luke Quintal)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5Ah 6S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Poison Arrow</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DUCK!</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4x Maytech 65162 brushless motors</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V (Withdrew) World Championship VI</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Duck DUCK DUCK! 2.0 (WC IV) DUCK! 3.0 (WC V)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Team Black and Blue</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Hal Rucker (Captain) Hannah Rucker Kathy Rucker (WC III, WC VI-BB: Champions I) Gabriel Stroud (WC IV) Eric Gever (WC IV) Julia Chernushevich (WC VI-BB: Champions I) Dave Lyons (WC VI-BB: Champions I) Piper Lyons (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Lifter</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bucktooth Burl , Red Devil , Ferocity , Marvin , HyperShock (Julia Chernushevich) Beta , Sabretooth (Gabriel Stroud)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>4x MaxAmps 4Ah 37V 150C LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>The Ringmaster , Marvin</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Daisy Cutter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2x Custom motors</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>World Championship IV</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Daisycutter</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Team Daisy Cutter a.k.a. Team Old Guys</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Bob Girardi (Captain) Anna Girardi Ken Girardi Gary Reynolds</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Huntington Beach, CA</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Vertical spinning disks</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Deadlift</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>T-MOTOR P80III KV100 motors</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>RoboGym Robotics</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ryan Shulski (Captain) Dan Tisza Mike Rouse Matt Birkel Alex Cuti</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Lifter Grappler (WC VI-BB: Champions I) Flamethrower</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Roundhouse , Snatch</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DeathRoll</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>243-250lbs</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship IV World Championship V (Withdrew) World Championship VII</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Death Roll DeathRoll 3.0 (WC V-Present)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Team DeathRoll</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Steven Martin (Captain) Jules Pitts Erica Hediger (WC II) Daniele De Biasio (WC II) Miles Blow (WC IV, WC VII-Present) Glen Rose (WC IV, WC VII-BB: Champions II)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Brisbane, Australia</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Vertical spinning disk</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>48V LiPo battery system</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Deep Six</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V (Withdrew) World Championship VI World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Team Overboard</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Dustin Esswein (Captain) Andrew Rossol Chris Carlson (WC IV) Trevor Tish (WC IV) Andrew Burghgraef (WC VI) Bradley Hanstad (WC VI) Chris Haataja (WC VI)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Norfolk, VA</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Vertical bar spinner</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bad Kitty , Chronos , Captain Shrederator (Bradley Hanstad) Warthog , Pardon My French (Chris Haataja) Lucky (Andrew Burghgraef) VD6.0 (Andrew Rossol, Bradley Hanstad) Lucky , Malice (Andrew Burghgraef) JackPot (Dustin Esswein, Chris Haataja, Bradley Hanstad)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>3.4Ah 6S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Triton</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Defender</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>4x Magmotors</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>World Championship VI</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Team Fast Electric Robots</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Jason Vasquez (Captain) Matt Vasquez Jeff Vasquez Debbie Vasquez Rob Masek Daisy Gonzalez</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Lifter/Grappler Flamethrower</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bite Force , Lucky , Scrap Metal , FrostBite (Rob Masek) Manta (Matt Vasquez) Valkyrie (Jason Vasquez) VD6.0 (Jeff Vasquez)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Whiplash , Splatter , Deb Bot , Matts Bammer , Think Tank</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Deviled Egg</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Recoil Robotics</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Zak Hassanein (Captain) Sydney Crump Shannon O'Hare Kathy O'Hare Stephen Jacobson Ryan Hasty</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Vallejo, CA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Drum spinner</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Sharko , Riptide (Zak Hassanein) Mega Tento (Ryan Hasty) Clockwork L'Orange (Shannon &amp; Kathy O'Hare)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Doom</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Team Bad Bot</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Mike Daniels Cody Daniels Eric Mueller "Mutt O'Matic" Patrick Fischer Tim Gendle Brandi Aders Theresa Eftink Jay Buie David Mims</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Titusville, CA</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Hinged wedge</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>NPC Charity Open</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Doomba</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2x Surpass 70120 brushless motors</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>World Championship VII (Alternate)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dooomba</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Team Hot Mess</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Brice Farrell (Captain) Thuong "Lou" Nguyen Brian Glatfelter Liz Chavarria Rudy Andriani Christopher Chamberlain Philippe Voyer Sharon Chamberlain</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Nottingham, MD</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Undercutting disk Flamethrower Lifting fork Axe Chainsaw</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Battle Royale With Cheese (Brice Farrell) Mammoth (Thuong Nguyen, Brice Farrell, Liz Chavarria) Sporkinok (Liz Chavarria) Pardon My French (Philippe Voyer)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Double Dutch</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>248½lbs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>World Championship II (Withdrew) World Championship III</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Iron LungFish Robotics</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Kevin Lung (Captain) Emmet Lung Dave Rhodes Michael Rhodes Frank Mueller</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Wadsworth, IL</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Twin horizontal bar spinners</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Chomp . Mongus , Spwack</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Double Jeopardy</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>248lbs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>World Championship II (Not selected) World Championship III World Championship IV World Championship V (Withdrew) World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Capital Punishment (WC II) Double Jeopardy 2020 (WC V-Present)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Team Double Trouble</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Evan Woolley (Captain) Bryce Woolley (Captain) Bill Woolley</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Irvine, CA</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Cannon</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>8Ah 25C LiPo battery</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Double Tap</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>World Championship VII (Alternate) BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DoubleTap</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Ostrich Air</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Jonathan Collazo (Captain) Neil Marek Derek Stevens Eric Carpenter Brian Sparano Arjen de Jong Avi Gileadi Jerome Strach Loren Carpenter Tod Powers John Rettie Daniel Wiggins Chris van Steyn Cory Ibanez Christian van Sloan Kevin Slattery Raymond W. Monroe Kenny Campbell Sasha Waxman Sterling Donner Andries van Overbeeke Christopher Margeson Jeffrey Gick</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Adjustable angled blade with centrifical hammers</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dragon King</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>World Championship VII (Alternate)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Bots Bash Party Crew</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Will Prater (Captain) Zach Lytle Diana Tarlson Leslie Shafton Robert Wisecarver Andy Sauro Sabrina Prater</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Birmingham, AL</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Crushing jaw Twin circular saws</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Slap 'Em Silly Slap 'Em Sillier Sledge-Jammer (Andy Sauro) Tombstone (Zach Lytle)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2026)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Skorpios</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dragon Slayer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC VII-Present) 2x NPC-T64 motors (WC VI)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>225-250lbs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>World Championship VI World Championship VII (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dragonslayer</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Wild Side Robotics</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Jordan Neal (Captain) Justin Kizer Dylan Halsey Josh Masseo</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Denton, TX</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Horns of Fury , Switchback (Jordan Neal)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2x Spektrum 5Ah 100c 4S LiPo batteries (vs. Minotaur) MaxAmps 9000XL 6S LiPo batteries (vs. DUCK!) 2x GensAce 7.5Ah 100c 4S LiPo batteries (vs. Blade and Uppercut) [ 2 ]</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Piranha</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Electric Ray</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>World Championship IV (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Team Robot Revolution</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Lucas Buermeyer Arnold Zhang</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Herndon, VA</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Twin horizontal bar spinners</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Ribbot (Lucas Buermeyer)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Emulsifier</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>World Championship V (Withdrew) World Championship VI (Not selected) World Championship VII</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bots FC</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Matt Bores (Captain) Ben Camphorst Adam Wrigley Eric Wrigley Paul Gancitano Mary Chimenti Kaycee Bores</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Columbus, OH</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Shatter! Bliss 2 Doomba and Friends</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>End Game</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4x 6374-192kV Motors</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>EndGame END GAME</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Team End Game (formerly OYES Robotics)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Jack Barker (Captain) Nick Mabey (Captain) Steven Barker Shane de Rijk (WC IV-BB: Champions II) Russell Barker (WC III-WC IV) Griffin Tabor (WC III) Devin Jerram (WC V) Emma McMillan (WC V-BB: Champions II) Christina Yu (WC VI-Present) Hammond Pearce (WC VI-BB: Champions II) Daniel Pound (BB Pro League 2026) Tim Sly (BB Pro League 2026) Connor Benton (BB Pro League 2026) Max Gruebner (BB Pro League 2026) Jolene Bedwell (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Auckland, AUK, New Zealand</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Mangō (Jack Barker) Bloodsport (Griffin Tabor)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2x 1.8Ah MaxAmps batteries</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Krusty Grab</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Extinguisher</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI (Not selected) World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Quicksilver Robotics</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>John Flaacke IV (Captain) John Flaacke III Patrick Gomez (WC IV) Brian Boatright (WC V) Ben Flaacke (WC V)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Tampa, FL</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Hammer Vertical spinner (WC V) Launcher (WC IV)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Gruff (John Flaacke IV)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Falcon</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2x Magmotors (NPC Charity Open-2009 Collegiate Championship)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>250lbs (WC IV) 120lbs (NPC Charity Open-2009 Collegiate Championship)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>World Championship I (Not selected) World Championship IV</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Falconizer (NPC Charity Open)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Team Whyachi Team Blue Devil (2009) Team Falcon (BBIQ 2004-BBIQ 2005)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Clint Ewert (Captain) Reese Ewert Lisa Ewert Terry Ewert Alex Boushon Eric Elmhorst Josh Matson Richard "Dick" Stuplich Logan Paul Tyler Paul Seth Runnoe Tommy Untiedt Andrew Venzke</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Dorchester, WI</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Twin drum spinners (WC IV) Single drum spinner (NPC Charity Open-2009 Collegiate Championship)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2004 NPC Charity Open R3: Rochester Robot Rampage 2005 Cisco Party 2006</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Hydra , Fusion , Red Square , Son of Whyachi , Warrior , Warrior Clan , Whyachi , Why Not , Y-Pout , YU812 , Falcon15 , Buzzkill</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Collegiate Championship 2009</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>BattleBots IQ 2004 BattleBots IQ 2005</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Foxtrot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4x TD6374 Motors</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>203lbs</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>World Championship IV</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Team Danby</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Craig Danby (Captain) Chris Danby Scott Kelly</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Raleigh, NC</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Lifter</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Switchback (Craig Danby)</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>4.5Ah 25C Nanotech LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Predator , Slammo! , Apex</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Free Shipping</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>250lbs (WC III-WC VI) 210lbs (WC VII-Present) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V (Withdrew) World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Team Special Delivery</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Gary Gin (Captain) Eric Gin Jim Yeh Forrest Yeh Roland Saekow Stephen Felk (WC IV) Chris Gin (WC III-WC IV) Michael Strange (WC VI-Present) Max Elvin (WC VII-Present) James Arluck (WC VII-Present) Ange Santaguida (WC VII-Present) Skye (BB FaceOffs)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>San Leandro, CA</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Lifter (WC III-BB: Champions I) Flamethrower Vertical spinner (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Voltronic , The Swarm (Stephen Felk) Lucky , Wipe Out #2 (Gary Gin) Yeti (James Arluck, Ange Santaguida) VD6.0 , Wrecks , Shockwave (James Arluck) Robo Master (Jim Yeh, Forrest Yeh) Agent X (Jim Yeh)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>The Big B</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Brushless motors</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Team Whyachi</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Reese Ewert (Captain) Richard "Dick" Stuplich Luke Ewert (WC VI-Present) Pedro Vela (WC VI-Present) Rachel Stuplich-Trantow (WC VI-Present) Trevor Trantow (WC VI-Present) Elizabeth Ewert (WC VI-Present) Terry Ewert</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Dorchester, WI</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Vertical spinner Horizontal spinner</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>New Cruelty , Bad Blood , Goosfraba Steel , Verbal Abuse (Richard Stuplich)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>18x 4S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Hydra , Son of Whyachi , Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Warrior Clan , Falcon , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GRABOT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>World Championship V</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Grabot</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Team DaStroy</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ben Davidson (Captain) Judah Davidson Matt Stroy Mike Stroy</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sheboygan, WI</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Grabbing arms Wedge</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gamma 9</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship V</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Gamma 9 from Outer Space (WC V)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Gamma Brigade</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Curtis Nemeth (Captain) Mike Okerman Dick Blummer Mike Blummer (WC III)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Huntington Beach, CA</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Crusher (WC III) Lifter (WC V)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BattleSaw (Curtis Nemeth)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Namreko 3000 , Gammatron , Gammacide</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4x AmpFlow motors (2x per half)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>250lbs (125lbs each)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship V</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fred (Red) Hydroxyl (Black) Free Radicals (Original collective name)</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Team Gemini (formerly Team Radicand)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Ace Shelander (Captain) Brentley Wiles (WC II) Greg Kress (WC II) Michael Chiasson (WC II) Scott Steber (WC II) Alan Debenedetti (WC II) Matt Walliser (WC III-WC IV) Andrew Kloface Lilibel de la Puente (WC III) Dominic Yankauskas (WC IV-WC V) Ben Hayton (WC IV) Lola Vars (WC IV) Hunter Yankauskas (WC V)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Joshua Tree, CA</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2x Horizontal spinners</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Slap Box (Dominic &amp; Hunter Yankauskas) Bolt , MacGuffin , ZAP (Ben Hayton)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ghost Raptor</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2x A28-150 AmpFlow motors</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>248lbs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship IV (Withdrew) World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Team Raptor</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Chuck Pitzer (Captain) Chris Harriman (WC I-WC II) Matt Herron (WC I-WC II) Vincent Cheung (WC I-WC II, WC V) Rachel Lucas (WC I-WC II) Darryl Dawson (WC I-WC II, WC V) Joel Meine (WC I-WC II) Eric Diehr (WC V-BB: Champions I) Sabri Sansoy (WC V-BB: Champions I) Xo Wang (WC VI-BB: Champions I) Anouk Wipprecht (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Articulated horizontal bar spinner Flamethrower (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Honest Abe (Xo Wang, Eric Diehr) Atomic Chile (Sabri Sansoy)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>8S 5Ah batteries</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Alpha Raptor , Tripulta Raptor , Pack Raptors , Carnage Raptor , W.L.O.W.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gigabyte</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors (WC VII-Present) 2x Short Magmotors (WC III-WC VI)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Robotic Death Company</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Derek Tran (Captain) (WC VI-Present) Camden Wallraff (Captain) (WC VI-BB: Champions II) John Mladenik Mike Lindberg Brent Rieker (WC III-Present) Carl Lewis (WC IV-WC V) Mark Liu (WC IV) Greg Rasche (WC IV) Jonathon Argueta (WC IV) Richard Loehnig (WC IV) Matt Maxham (WC V-BB: Champions I) Wendy Maxham (WC V-BB: Champions I) Thy Phi (WC V-BB: Champions I) Elizabeth Mladenik (WC V-Present) Melissa Mladenik (WC V-Present) David Janssen (WC V) Anouk Janssen (WC V) Josh Hicok (WC V) Carol Williams (WC V-Present) Micah "Chewy" Leibowitz (WC VI-Present) Alon Belkin (WC VI-BB: Champions I, BB Proving Ground) Conor O'Brien (WC VI-BB: Champions I) Jerry Serafin (WC VI-BB: Champions I) (WC VI-Present) Blair Lindberg (WC VI-Present) Sam Smith (WC VII-Present) Dave Moulds (WC VII-Present) Cal Coker (WC VII-Present) Jesse Ramos (WC VII-Present) Adam Stewart (WC VII-Present) Lacy Stewart (WC VII-Present) Eric Fisher (WC VII-Present) Sri Ram Nervati (WC VII-Present) Michael Parks (BB Proving Ground) Alex Price (BB Proving Ground)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Oceanside, CA</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Shell spinner</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Stinger: The Killer Bee , Devil's Plunger , Sewer Snake , Wipe Out #2 (Matt Maxham, Wendy Maxham) Wrecks , Skorpios (Micah Leibowitz) Chronos , No Luv , El Cucuy , Bit Schlapp (Jerry Serafin) Horizon (Alon Belkin, Alex Price) Calypso (Alon Belkin, Alex Price, Derek Tran) Axolotl (Alon Belkin) Lucky (David Janssen, Anouk Janssen) The Disk O' Inferno (Richard Loehnig, Mark Liu) Tiki Fire (Micah "Chewy" Leibowitz) Taco Tuesday (Camden Wallraff) JackPot , Manta , Goldenn Fury (Derek Tran) Banshee (Alex Price, Alon Belkin) Nemesis (David Le)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Megabyte , Rambite , Invader , Cobalt , Super Megabyte , Agsma</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Glitch</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4x Scorpion SII-4035-450KV motors</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Combat Robotics at Berkeley</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Kyle Miller (Captain) Anthony Moody Katie How Ray Hufnagel (WC VI-BB: Champions I) Roy Zhang Yoonji Kwon (WC VI-BB: Champions I) Andrei Dones (WC VI-BB: Champions I) Andy Ngo (WC VI-BB: Champions I) Andy Lin (WC VI-BB: Champions I) Anna Hagiwara Carl Matabang (WC VI-BB: Champions I) Emma Guo (WC VI-BB: Champions I) Helena Greebe (WC VI-BB: Champions I) Henry Chen Kaitlyn Lee Karen Ting Larry Zhao (WC VI-BB: Champions I) Lauren Lee Lekha Duvvoori Matthew Mena (WC VI-BB: Champions I) Mona Li (WC VI-BB: Champions I) Romy Mastel Thomas Wang (WC VI-BB: Champions I) Vincent Le (WC VI-BB: Champions I) Kabir Daniel (WC VI-BB: Champions I) Ishaan Gupta (WC VII-BB: Champions II) Blake Werner (WC VII-BB: Champions II) Catherine Jin (WC VII-BB: Champions II) Claire Wang (WC VII-BB: Champions II) Henry Tsai (WC VII-BB: Champions II) Luan Chuang (WC VII-BB: Champions II) Lucero Jones-Ortiz (WC VII-BB: Champions II) Makayla Connelly (WC VII-BB: Champions II) Mingyang Wang (WC VII-BB: Champions II) Ranjini Nair (WC VII-BB: Champions II) Shrey Aeron (WC VII-BB: Champions II) Suchith Palyam (WC VII-BB: Champions II) Taylor Waddell (WC VII-BB: Champions II) Troy Keslinke (WC VII-BB: Champions II) Willem Kuenen (WC VII-BB: Champions II) Ivan Hendry (WC VII-BB: Champions II)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Roseville, CA</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Eggbeater drum spinner</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Axolotl (Ishaan Gupta)</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>10S 6.5Ah LiPo battery (WC VII-BB: Champions II) 8S 8Ah LiPo battery (WC VI-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Holy CR@B , Thunderstorm</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gruff</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4x Ampflow E30-400 brushed motors (WC IV)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Gruff the Mighty Dragon (WC IV) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Team Gruff</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sam McAmis (Captain) Chuck Butler Jeremy Butler Jason Ryan Marcello Mennone (WC V-Present) Stephen Chapman (WC VI-Present) Vinny McAmis (WC V-Present) Hugh Savoldelli (WC VI-Present) John Flaacke IV (WC VII-Present) Jason Rogers (WC VII-BB: Champions II) Ben Murphy (WC VII-Present) David Raditch (WC IV) Melissa McAmis (WC IV) Max McAmis (WC IV)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Palm Harbor, FL</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Lifting forks Flamethrowers Hammer (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Quasar (Sam McAmis) Extinguisher (John Flaacke IV) Slammo! (Jason Rogers)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HUGE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless motors</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Team HUGE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Jonathan Schultz (Captain) Peter Lombardo Maddie Thumma Garrett Santoline Don Doerfler (WC IV-Present) Alex Horne (WC III, WC V) Joe Doerfler (WC VII-Present) Brendan Steele (WC VII-Present) Kathryn Allen (BB Pro League 2026) Rory Mangles (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>South Windsor, CT</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Vertical bar spinner</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Big Dill (Tommy Wong) Monsoon , Predator , Two-Headed Death Flamingo (Rory Mangles)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>12x 6S 2.8Ah LiPo batteries [ 1 ]</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HiJinx</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2x Castle 1515 brushless motors</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>242-250lbs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hijinx Kestrel (Working name)</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Offbeat Robotics</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Jen Herchenroeder (Captain) Orion Beach Madeline Hagan Chestley Couch (WC V-BB: Champions I) Tim Bogdanof (WC V) Chas Leichner (WC VI-Present) Michael Cox (WC V-BB: Champions I) Matthew Garrett (WC V-BB: Champions I) Paloma Fautley (WC VI-Present) Eli D'Elias (WC V-BB: Champions I) Jackie Gerstein (WC VII-Present) Geno Esposito (WC VII-Present) Zack Robinson (WC VII-Present) Cameron Schaefer (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Oakland, CA</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Battle Royale With Cheese (Jen Herchenroeder) Skorpios (Orion Beach, Jen Herchenroeder) Bite Force (Tim Bogdanof) Wrecks (Orion Beach)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2x 6S Tattu R-Line 22.2V Gens Ace 5.1Ah LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (Withdrew)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Skorpios</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2x TP5680 Brushless inrunner motors</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>225lbs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>World Championship VI (Not selected) World Championship VII</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions II (Withdrew)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Horizon250 Horizon 2022 (WC VII) Ganymede (Concept name) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Team Horizon</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Joshua Kong (Captain) Alon Belkin Kyle Loyola Dylan McKenzie Alex Price Alicia Garnache (WC VII) Peter Garnache (WC VII) Conor O'Brien Justin Nyam Kai Yin Tommy Wong (WC VII-Present) Victoria Tomozei (BB Proving Ground 2023)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Continuous horizontal hammer saw</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Cobalt (Alon Belkin, Conor O'Brien) Gigabyte (Alon Belkin, Alex Price, Conor O'Brien) Axolotl (Alon Belkin, Victoria Tomozei) Chronos , Valkyrie (Kyle Loyola) Big Dill (Tommy Wong) Malice (Peter Garnache) SHREDDIT BRO! (Alicia Garnache) JackPot , Project Aegis , Altair , Category 5 (Joshua Kong) Terrortops , DOOM (Victoria Tomozei)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>8S 5100mAh LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Calypso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Hydra</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>4x Brushless motors</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2022)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>HYDRA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Team Whyachi</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Jake Ewert (Captain) Richard "Dick" Stuplich Rachel Stuplich-Trantow (WC V-Present) Terry Ewert</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Dorchester, WI</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Hydraulic flipper</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>New Cruelty , Bad Blood , Goosfraba Steel , Verbal Abuse (Richard Stuplich, Rachel Stuplich-Trantow)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>BattleBots: Destruct-A-Thon</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Son of Whyachi , Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Warrior Clan , Fusion , Falcon , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>HyperShock</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2x NeuMotor 8038 motors</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>238-250lbs</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hypershock</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Team HyperShock (formerly Shenanigans &amp; Co.)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Will Bales (Captain) Kyle Awner (WC III-Present) Isaac Lubarsky (WC III-BB: Champions I) Greg Bales (WC V-Present) Max Bales (WC VI-BB: Champions II) Tyler Bond (WC I-WC V) Alex Mattaway (WC I-WC III) Cameron Cecil (WC I) Kat Cochran (WC IV-BB: Champions II) Derrick Deville (WC IV, WC VI-BB: Champions I) Gary Nguyen (WC V-Present) Collin Royster (WC V-BB: Champions II) Alex Bales (WC VI-Present) Natalie Royster (WC VI-BB: Champions II) Connie Ryan (WC VI-Present) Julia Chernushevich (WC VII-Present) David Rodriguez (BB Proving Ground-Present) Isabella Oskarsson (BB Proving Ground) Andreas Thurn (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Vertical spinner Hydraulic arms (WC I) Lifting wedges (WC II) Grabbing/Crushing jaws (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Mohawk (Greg Bales, Max Bales, Connie Ryan, Kat Cochran) Fluffy , Fluffy DeLarge , El Cholo , SpiderPig , X-Termination , The Woodynator , X-Contamination , X-Mutilation , Über Schnitzel , Brute Force , X-Revolution , X-Fortification , X-Evolution , X-Assassination , ThaiTanium , Coriolis (Will Bales, Kyle Awner, Tyler Bond, Alex Mattaway) DUCK! , Marvin , Bucktooth Burl , Red Devil , Ferocity (Julia Chernushevich) ROTATOR (Gary Nguyen)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>6x 8S 3Ah SMC Racing LiPo batteries (WC VI) 6x 8S 3.3Ah Thunder Power LiPo batteries (re:MARS 2022-Present)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023) BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Hot Mess , Vertigo</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hypothermia</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2x AmpFlow 48V motors</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>231½-248lbs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>World Championship III</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Team Toad</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Michael "Fuzzy" Mauldin (Captain) Kay Mauldin Tony Woodward Jon Bennett</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Liberty Hill, TX</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Grabbers Lifter</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Skorpios (Tony Woodward)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>MaxAmps 36V LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Texas Twister , El Furro , Ice Chip , TadPole , SnowCone , WindChill , IceCube , SnowFlake , IceBerg , FrostBite</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Icewave</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2x Magmotors</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>250lbs (WC I-Present) 120lbs (2004-2007)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship VI World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BattleBots IQ 2004 2004 NPC Charity Open BattleBots IQ 2005 BattleBots IQ 2006 Cisco Party 2006 BattleBots at Java One re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ICEwave Goliath (BBIQ 2004)</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Team Icewave (WC I-WC VI) Team UI (BBIQ 2004-JavaOne 2007)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Marc DeVidts (Captain) Angela Bamblett Alex Espinosa (WC III, BB: Bounty Hunters-WC VI) Michael Turner (BB: Bounty Hunters-WC VI) Jamie Price (WC VI) Michael Macht (WC VI) Andrew Adams (WC I-WC II)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Burlingame, CA (formerly Sunnyvale, CA)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>ROTATOR (Marc DeVidts) Afterburner , Turbo , Surgeon General (Alex Espinosa) Moebius , Phishfeuxd (Michael Macht)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2x 6S 5Ah LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Edge , Vault</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JackPot</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>243-250lbs</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sabertooth (Original name) Jackpot 777 JackPot (WC VII)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Vegas Combat Robotics</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Jeff Waters (Captain) Robert Stehn Shea Johns Chris Haataja (WC V) Jason Woods (WC VI-Present) Lucas Grell (WC VI-Present) Kat Waters (WC VI-Present) Law Laxina (WC VII-Present) Zach Church (BB Proving Ground-Present) Derek Tran (BB FaceOffs 2025) Cindy Lu (BB FaceOffs 2025) David Le (BB FaceOffs 2025) Grace Thomas (BB FaceOffs 2025) Dustin Esswein (BB Pro League 2026) Scott Johnston (BB Pro League 2026) Steven Shaffer (BB Pro League 2026) Aaron Taggart (BB Pro League 2026) George Gutierrez (BB Pro League 2026) Sam Gallagher (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Vertical spinner Lifting forks (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Warthog , Pardon My French (Chris Haataja) Tracer , Slingshot , Rebob (Jason Woods) Switchback , Max Q (Shea Johns) Banshee (Jeff Waters) Traves T. (Zach Church) Calypso (Derek Tran, Cindy Lu) Cobalt , Gigabyte (Derek Tran, David Le) Manta , Golden Fury (Derek Tran) Nemesis (David Le, Grace Thomas) Deep Six (Chris Haataja, Dustin Esswein) Malice (Scott Johnston) Triton (Sam Gallagher)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>24x 4S 1.55Ah LiPo batteries (WC VII-Present) 12S 10Ah LiPo batteries (WC V-re:MARS 2022)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023) BattleBots FaceOffs (2024) BattleBots Proving Ground (2025) BattleBots FaceOffs (2025)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Jasper</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4x Ampflow A28-400 brushed motors [ 1 ] [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>World Championship IV</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Tomco Designs</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Tom Lloyd (Captain) Sabrina Ferriggi Kevin Cleasby Tate Kapple Cristy Aranguiz</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Radioactive , X/Change (Kevin Cleasby)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jäger</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>246lbs (Combined)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>World Championship V (Withdrew) World Championship VI World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Jager</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Team Jäger</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Ralf Schneider (Captain) Andy Russell Cosmin Gorgovan Jonas Fink Charlie Dangerfield Ed Hodges</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Gemünden, BAV, Germany &amp; United Kingdom</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Undercutter Hammer saw Drum spinner (unused)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Nelly the Ellybot (Charlie Dangerfield) Big Dill (Andy Russell, Emmanuel Carrillo) Abrasion (Ed Hodges)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kingpin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V (Withdrew) World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Team Burntpopcorn</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Kevin Hjelden (Captain) Steve Hjelden</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sacramento, CA</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4x HyperDrive motors (WC VII-Present) 2x NPC-T74 motors (WC III-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>249lbs</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Kraken v2 (WC VII-Present) The Kraken</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CE Robots</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Matt Spurk (Captain) Michael Spurk Sara Spurk (WC III-WC IV, WC VI-Present) Cayden Spurk (WC III-WC IV, WC VI-Present) Ethan Spurk (WC III-WC IV, WC VI-Present) Stephen Spurk (WC III-WC IV, WC VII-Present) Peggy Spurk (WC III-WC IV, WC VI-Present) Wesley Wood (WC III-WC IV, WC VII-Present) John Summers (WC IV-Present) Jill Mucci (WC IV, WC VI-Present) Zoe Jane Whitfield (WC IV, WC VI-Present) Todd Garrett (WC IV, WC VI-Present) Melissa Mendoza (WC IV) David Wickers (WC VII-Present) David Ritland (WC VII-Present) Jeremy Silliman (WC VI-Present) Slane Parsons (WC VII-Present) Barbara Wilson (WC VII-Present) Kimi Silverman (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Titusville, FL</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Crusher Articulating vertical spinner (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Lock-Jaw</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>4x Ampflow-A28-250 motors</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lock Jaw Lockjaw</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Mutant Robots</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Donald Hutson (Captain) Paul Ferrell Jonathan Medina Alex Kozarev Walter Maksimow (WC II-Present) Allie Levy (WC III-Present) Reginald Wilson (WC V-Present) Dylan Walter (WC VI-BB: Champions I) Logan Davis (WC VII-Present) Brady Davis (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>San Diego, CA</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Grabbing jaws (WC I-WC III) [ 1 ] Flamethrower (WC I-WC III) Spring flipper (WC II) Vertical bar spinner (WC II) Vertical disk spinner (WC III-Present)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>SubZero (Reginald Wilson, Logan Davis, Brady Davis) Texas Twister (Brady Davis) Switchback (Logan Davis) ShazBot (Donald Hutson)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>17Ah LiFePO batteries (6-8S)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>CU-JAW , Diesector , Tazbot , Easty Beast , Root Canal , Gear Crow</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2x Magmotors</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship V (Withdrew) World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LUCKY!</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>TKO Robotics (formerly Team Lucky Canucky )</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Mark Demers (Captain) Jeff Hayashida Rob Frankovich Matt Bailey Tim Bayne David Kennedy (WC II, WC IV-Present) Zac O'Donnell (WC II) Gary Gin (WC II) Rob Masek (WC II-WC IV) Dave Solomon (WC II-WC IV) Jerome Johnson (WC II-WC IV) Daniel Suchomel (WC II-WC IV) Roland Saekow (WC II) Kurtis Wanner (WC III) Andrew Burghgraef (WC III-WC IV) Ben Hei (WC IV-BB: Champions I) Reza Kazemi (WC III-WC IV) David Janssen (WC IV-BB: Champions I) Tom Burn (WC IV, WC VII-Present) Mohan Gurunathan (WC VI-Present) Matt Olson (WC VI-Present) Anouk Janssen (WC VI-Present) Megan Melton (WC VII-Present) Thacia Frank (WC VII-Present) Marcelo Borges (WC VII-Present) Igor Duran (WC VII-Present) Todd Cope (WC VII-Present) Karolina Ash (WC VII-Present) Bennet Heidenreich (WC VII-Present) Luc Goldstein (WC VII-Present) Landon Spaw (WC VII-Present) Jennifer Lynn (WC VII-Present) Rodney Hansen (WC VII-Present) Martin Coursol (WC VII-Present) Cassandra Coursol (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Ottawa, Canada</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Launcher</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Free Shipping , The Big B , Wipe Out #2 (Gary Gin) Captain Shrederator (Zac O'Donnell) Defender , Bite Force , FrostBite , Scrap Metal (Rob Masek) Deep Six , Triton , Malice (Andrew Burghgraef) Witch Doctor , Hack &amp; Slash (Kurtis Wanner) BravePart , PitBot (Mark Demers, Jeff Hayashida, Mohan Gurunathan, Robert Frankovich, Jerome Johnson) Cobalt (Matt Olson, Mark Demers) Nerd Killer , Shockwave , VD6.0 , Wrecks , Yeti (James Arluck)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground BattleBots FaceOffs</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Ziggy , CycloneBot</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MadCatter</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>6x 9kW Brushless motors</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Mad Catter MaDCatTer</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Team Bad Kitty</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Martin Mason (Captain) Calvin Iba (WC IV-Present) Allen Phuong Thomas Thomas (WC IV-BB FaceOffs 2024) Emmanuel Carrillo (WC IV) Kenny Hu (WC IV-BB: Bounty Hunters, BB Pro League 2026) Ryan Lau (WC IV-BB: Bounty Hunters, WC VII-Present) Zack Jafery (re:MARS 2022-Present) Ralph Hanson (WC VII-Present) Misael Macedo (WC VII-BB: Champions II) Jeremy Germita (WC VII-BB: Champions II) Coleman Christy (WC VII-Present) Wesley Socia (BB Pro League 2026) Joey Kadin (BB Pro League 2026) Dylan Woessner (BB Pro League 2026) Chris Miko (BB Pro League 2026) Maria Galvan (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Pomona, CA</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Vertical spinner Axe (WC IV-BB: Bounty Hunters) Lifting arm (WC IV-WC VII)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Big Dill (Emmanuel Carrillo, Ryan Lau) WAR Hawk , Jäger (Emmanuel Carrillo) Calypso (Wesley Socia, Dylan Woessner, Joey Kadin)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>5Ah 6S LiPo batteries (WC IV-Present) 3.3Ah/4Ah LiPo batteries (WC IV-BB: Bounty Hunters) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Bad Kitty , CatKong</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Malice</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2x S28-D4-400x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters re:MARS all:STARS (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Team Malice</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Adrian "Bunny" Liaw (Captain) David Liaw David Rush David Small (WC V-BB: Champions I) Nick Dobrikov (WC V-BB: Champions II) Isaak Malers (WC VI-BB: Champions II) Mike Britton (WC VII-BB: Champions II) Brian Adamson (WC VII-Present) Ray Billings (WC VII-BB: Champions II) Jonathan LaPlain (WC VII-BB: Champions II) Johnny Tsoumpas (BB FaceOffs-Present) Alex Tramiel (BB FaceOffs-Present) Peter Garnache (BB FaceOffs-Present) Scott Johnston (BB FaceOffs) Josh Adriano (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Horizontal drum spinner</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Wrecks , Shatter! (Adrian "Bunny" Liaw) Silver Shield (David Liaw) Big Dill (Isaak Malers) Banshee (David Small, David Rush) Drago (Nick Dobrikov) Skorpios (Adrian "Bunny" Liaw, David Liaw, Jonathan LaPlain) Doomba and Friends (Adrian "Bunny" Liaw) Tombstone , Swamp Thing , Darkness , The Raven , Skorpios (Ray Billings) Captain Shrederator (Jonathan LaPlain) Horizon (Peter Garnache) VD6.0 (Alex Tramiel) JackPot (Scott Johnston)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Mammoth</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2x RV-100 motors</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Team Mammoth</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Ricky Willems (Captain) Brice Farrell Thuong "Lou" Nguyen Matt Bailey Courtney Hollis Anna Goodridge Audrey Van de Castle (WC IV-BB: Bounty Hunters) Lizzy Ostrowski (WC IV-BB: Bounty Hunters) Ellie Rose (WC VII-Present) Aaron Bard (WC VII-Present) Anna Goodridge (WC VII-Present) Cody Graham (WC VII-Present) Courtney Hollis (WC VII-Present) Zoe Lambert (WC VII-Present) Em Ostrowski (WC VII-Present) Ellie Weinstein (WC VII-Present) Brandon Young (WC VII-Present) Liz Chavarria (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Baltimore, MD</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Rotary lifting trunk Flamethrower (WC IV)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Battle Royale With Cheese (Brice Farrell) Doomba (Brice Farrell, Thuong "Lou" Nguyen, Liz Chavarria)</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Mecha Rampage</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>World Championship III</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>C2 Robotics (formerly Team Coolrobots)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Christian Carlberg (Captain) Mike Ballard Jessica Carlberg Carissa Carlberg Coen Carlberg Riesen Carlberg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>San Luis Obispo, CA</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Yeti , Chunk (Christian Carlberg)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>OverDrive , Minion , OverKill , Toe-Crusher , Dreadnought , Knee-Breaker , UpperCut , TriDent , Nasty , Little Killer</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4x Maytech 6374 brushless motors</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>250lbs (WC IV-WC V) 235lbs (WC VI)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>P1 Evo (WC V) P1 LM (WC VI)</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Aberrant Robotics</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Brandon Zalinsky (Captain) Luke Bittenbinder J.T. Atkinson (WC IV-WC V) Sam Mills (WC IV-WC V) Sarah Pohorecky (WC V-WC VI) Amelia Godolphin (WC IV) Briana Vollbeer (WC IV) Alex Garver (WC IV) Rory Charlesworth (WC V) Anthony D'Ambrosio (WC VI)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Hudson, NH (WC V-WC VI) Clemson, SC (WC IV)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Front-hinged lifter</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Uppercut (Sarah Pohorecky) Starchild , RIPperoni (Brandon Zalinsky, Sarah Pohorecky)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Parallax , Talos</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Pain Train</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Team Shreddit</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Evan Arias (Captain) Anthony D'Ambrosio Debbie Pena (WC V) Raul Pena (WC V) Gennadiy Katsman (WC VI) Thy Phi (WC VI) Angel Vidal (WC VI) Brandon Unger (WC VI) Amanda Brickner (WC VI) Drew Davis (WC VI) Alessanda Mangialardo (WC VI)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Staten Island, NY</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Eggbeater drum spinner</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>SMEEEEEEEEEEEEE (Brandon Unger) Starchild , RIPperoni (Anthony D'Ambrosio)</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>3x 5Ah 45C LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>SHREDDIT BRO!</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Perfect Phoenix</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>169-230lbs</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VII (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Team Doom Robotics</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Tyler Nguyen (Captain) Juli Johnson Teri Billings (WC V) Scottie Riddle (BB: Champions I) Ray Billings Justin Billings (BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Herndon, VA</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Tombstone , Malice (Ray Billings) Brutality (Alternative identity)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Rampage</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4x AmpFlow E30-400 motors</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>245lbs</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII (Not selected)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Team X</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Daniel Knox (Captain) Melaina Knox Devin Knox Christian Knox Curtis Knox Ethan Knox George Knox</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Port St Joe, FL</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>4x Turnigy Nanotech 5Ah 5S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ribbot</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2x S28-150 Magmotors</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Team Ribbot (formerly Team WPI)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Nick Sorensen (Captain) David Jin (WC IV-WC VII) Christian Cooper (WC IV-WC VII) Tim Bell Andrew Mularoni (WC IV-WC VII) Zeke Andreassen (WC IV-WC VII) Alex Johnson (WC V-WC VII) Lucas Buermeyer (WC V-Present) Nick Hom (WC V-Present) Karl Ehlers (WC IV-WC V, BB Pro League) Danny Lu (WC IV-WC V) Cam Collins (WC IV-WC V, BB Pro League) Madison Healey (BB Pro League 2026) Allison Koran (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Boston, MA</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Vertical disk spinner Horizontal undercutter Vertical bar spinner Lifter (WC IV) Eggbeater spinner (BB BB Pro League)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Electric Ray (Lucas Buermeyer)</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Rotator</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rusty</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI World Championship VII (Alternate)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I (Withdrew)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Rusty Mk.I (WC V-VI) Rusty Sr. (WC V-VI) Rusty Mk.II (WC VI-Present) Rusty Jr. (WC VI-Present)</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Team Iron Force</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Dave Eaton (Captain)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Antioch, IL</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Jackhammer Sledgehammer Lifter</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SMEEEEEEEEEEE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SawBlaze</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2x T&amp;P brushless motors 2x Black Max motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sawblaze</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Team SawBlaze (formerly LiMITless Robotics)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Jamison Go (Captain) John Mayo (WC II-WC VI) Lucy Du (WC III-WC VI) Joao Ramos (WC II-WC IV) Chris Merian (WC II-WC III) Alex Hattori (WC III) Mason Massie (WC III) Jake Chesin (WC IV-Present) Raymond Ma (WC IV-Present) Shakti Shaligram (WC IV-Present) Kim Jung (WC IV-WC V) Patrick McKeen (WC IV) John Romanishin (WC IV) Samantha Chapin (WC V-Present) Stephanie Chesin (WC VI-Present) Aaron Fan (WC VII-Present) Samantha Glassner (WC VII-Present) Liam Chapin (WC VII-Present) Eli Davis (WC VII-Present) Alina Granville (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Articulating overhead saw Hammer saw (WC III-Present) Flamethrower</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Overhaul (Jamison Go, Lucy Du) Road Rash , Uppercut (Alex Hattori) Valkyrie (Lucy Du)</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>MaxAmps 14.4v 13.5Ah Custom LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>BattleBots: Destruct-A-Thon</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sharko</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2x MC160 motors</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>220lbs</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV (Exhibition only) World Championship V</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Sharkoprion (WC III-WC IV)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Aquatic Machine Force</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Edward Robinson (Captain) John Hoffman (WC III-WC IV) Zak Hassanein (WC V-BB: Bounty Hunters) Dominic Borg (WC V-BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Jacumba, CA</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Thwacking tail Vertical spinner (WC III-WC IV) Flipper/Grappler (WC V)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Deviled Egg , Riptide (Zak Hassanein) P.T. Bruiser , Robot X (Edward Robinson)</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Mantasaur , TriloBot</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Shatter!</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>4x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SHATTER! Shatter</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bots FC</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Adam Wrigley (Captain) Eric Wrigley Mary Chimenti Paul Gancitano Adrian "Bunny" Liaw (WC IV) Matt Bores (WC IV, WC VII-Present) Ben Camphorst (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Hammer Sword (WC VI-Present)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Exergy (Adam Wrigley) Malice , Wrecks , Doomba and Friends (Adrian "Bunny" Liaw)</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Emulsifier Doomba and Friends Bliss 2</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Skorpios</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC II - WC IV) 4x Short Magmotors (WC V-BB: Champions II) 2x Long Magmotors &amp; 2x Small Magmotors (WCVIII-Present)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>~250lbs</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Bot Bash Party Crew (formerly Offbeat Robotics )</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Zach Lytle (Captain) Diana Tarlson (Captain) (WC III-Present) Jerry Serafin (WC II) Orion Beach (WC II-WC IV) Max Maruszewski (WC II-WC III) Micah Leibowitz (WC II-WC IV) Dan Chatterton (WC III-BB: Champions I) Jen Herchenroeder (WC IV) Ben Shafton (WC IV-Present) Adam Duarte (WC IV) Bennett Funk (WC IV-BB: Champions I) Kayen Duarte (WC IV) Leslie Shafton (WC V-BB: Champions II) Shannon Tobin (WC V-BB: Champions I) Robert Wisecarver (WC V-Present) Allan Cecil (WC VI-BB: Champions II) Tony Woodward (WC VI-BB: Champions I) Will Prater (WC VI-BB: Champions II) Adrian "Bunny" Liaw (re:MARS all:STARS 2022) Jeff Waters (re:MARS all:STARS 2022) Shea Johns (re:MARS all:STARS 2022) Jonathan LaPlain (re:MARS all:STARS 2022) Andy Sauro (WC VII-BB: Champions II) Ray Billings (BB FaceOffs) Daniel Granicher (BB FaceOffs-Present) Jesse Roberts (BB FaceOffs-Present) Ezra Pramono (BB FaceOffs-Present) Ethan (BB FaceOffs) Leif Hasle (BB FaceOffs-Present) Scott Siegel (BB Pro League 2026) Charlie Siegel (BB Pro League 2026) Alexis Debusschere (BB Pro League 2026) Bob Roberts (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Moraga, CA</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Articulating overhead saw Hammer saw (WC IV-Present) Articulating flamethrower fangs (WC V) Overhead flamethrower (WC VII-Present) Overhead swinging knife (WC VII-Present)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Wrecks (Micah Leibowitz, Dan Chatterton, Orion Beach, Adrian "Bunny" Liaw) HiJinx (Jen Herchenroeder, Orion Beach) Gigabyte , No Luv , El Cucuy , Bit Schlapp (Jerry Serafin) Battle Royale With Cheese (Jen Herchenroeder) Cobalt (Micah Leibowitz, Jerry Serafin) Hypothermia , Texas Twister (Tony Woodward) Malice (Adrian "Bunny" Liaw, David Liaw, Ray Billings) JackPot (Jeff Waters, Shea Johns) Captain Shrederator (Jonathan LaPlain) Shatter! , Doomba and Friends (Adrian "Bunny" Liaw) Swamp Thing (Adam &amp; Kayden Duarte) Tiki Fire (Micah Leibowitz) Slap 'Em Silly , Slap 'Em Sillier , Sledge-Jammer (Andy Sauro) Tombstone , Mortician , Swamp Thing , Darkness , The Raven (Ray Billings) Calypso (Daniel Granicher) Nemesis (Bennett Funk)</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>MaxAmps LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>BattleBots Proving Ground (2023) BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Dragon King</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SlamMow!</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Slap Box</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>World Championship V</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SlapBox</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Team Already Broke</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Bryce Yankauskas (Captain) Cynthia Yankauskas Dominic Yankauskas Hunter Yankauskas Onika Yankauskas</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Knox, IN</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Lifter Flamethrower</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Gemini (Dominic Yankauskas, Hunter Yankauskas)</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Son of Whyachi</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>4x Astro 90 Cobalt motors</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>250lbs (WC I-Present) 315lbs (Season 3.0-5.0)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2004 NPC Charity Open BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SOW S.O.W. Nitro SOW</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Team Whyachi</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Terry Ewert (Captain) Luke Ewert (Captain) (WC II-WC IV) Reese Ewert (WC II-WC IV, BB: Bounty Hunters) Elizabeth Ewert Richard "Dick" Stuplich (WC II) Rachel Stuplich-Trantow (WC IV) Jake Ewert (Comedy Central, BB: Bounty Hunters)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Dorchester, WI</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Horizontal tri-bar spinner</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>New Cruelty , Bad Blood , Verbal Abuse , Goosfraba Steel (Richard Stuplich, Rachel Stuplich-Trantow)</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Various 4S and 5S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Hydra , Fusion , Falcon , Warrior Clan , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Season 3.0 Season 4.0 Season 5.0</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Sporkinok</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>4x 6474 Brushless motors</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Team PRIDE</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Lilith Specht (Captain) Andrew Rudolph Liz Chavarria Nick Polanoski</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Orlando, FL</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Flipper Spork hammer</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Doomba (Liz Chavarria)</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SubZero</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>250lbs (WC II-Present) 220lbs (2009 Pro Championship) 140lbs (NPC Charity Open-JavaOne 2007)</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>World Championship II World Championship III World Championship IV World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Cisco Party 2006 BattleBots: Bounty Hunters BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Subzero</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Team Hammertime (NPC Charity Open-WC IV) Team XD (WC V-WC VI)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Team Hammertime Jerry Clarkin (Captain) Logan Davis (WC II-WC III) Alex Horne (WC II, WC IV) Brady Davis (WC II-WC III) Reginald Wilson (WC II-WC III) Chris Feiock (WC IV) Jon Durand (NPC Charity Open-Cisco Party) Team XD Logan Davis (Captain) Brady Davis Mitch Cerroni Brian Bray Kris Mitchell (WC V) David Baker (WC VI)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Team Hammertime Malvern, PA Team XD Dallas, TX</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Pneumatic flipper</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Lock-Jaw (Reginald Wilson, Logan Davis, Brady Davis) The Cone Army , Mixmaster (Alex Horne) Texas Twister (Brady Davis) Mudhole Bullfrog , Total Anarchy (Jon Durand) Switchback (Logan Davis)</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2004 NPC Charity Open R3: Rochester Robot Rampage BattleBots JavaOne 2007</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Team Hammertime Hammertime , Bounty Hunter Team XD Steel Reign , HazMatXD , Adonai , RobotussinDM , ...Tysant</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Pro Championship 2009</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Tantrum</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>250lbs (WC IV-Present) 235lbs (WC III)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Seems Reasonable Robotics</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Ginger Schmidt (Captain) Alex Grant (Captain) Aren Hill Sean Doherty Erica Chin Jason Weihman Brian Silverman Bryan Culver (WC IV-Present) Dillon Carey (WC IV-Present) David Mintz (WC IV-Present) James Doherty (WC IV-Present) Zach Marks (WC V-BB: Champions II) William Stanley (WC V-Present) Alec Kochis (WC VI-Present) Max Chang (WC VI-Present) Sue Doherty (WC VI-Present) Katie Widen (WC VI-Present) Kristine Atiyeh (WC VI-Present) Steven Silverman (WC VI-Present)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Mountain View, CA</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Punching vertical spinner (WC IV-Present) Spring flipper (WC III)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Insult and Injury (Aren Hill, Jason Weihman, Bryan Culver)</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>4x 5.4Ah 6S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Blip , The Twins</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>The Four Horsemen</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Various Ranglebox motors</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>~250lb combined</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Four Horsemen</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>The Four Horsemen</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Ian Watts (Captain) Sam Watts Ann Gribble Jamie Anderson (WC IV) John Frizell (WC IV) Ryan Pratt (WC III)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Brighton, UK</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Various horizontal spinners</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>5S LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Creepy Crawlies , Bull Dog , Little Sister</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Tombstone</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless outrunners</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>220lbs (Pro Championship 2009) 250lbs (WC I-Present) 340lbs (NPC Charity Open)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII (Withdrew)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2004 NPC Charity Open re:MARS all:STARS (2019) BattleBots: Bounty Hunters re:MARS all:STARS (2022) BattleBots: Champions I BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Hardcore Robotics</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Ray Billings (Captain) Rick Russ (WC I-BB: Champions I) Justin Billings Brittney Billings (WC II, WC VI-Present) Lorna West (WC V-BB: Champions I) Susan Billings (WC II) Roy Hellen (WC V-BB: Bounty Hunters) Tyler Nguyen (WC V-BB: Champions I) Kevin Benesi (WC VI-Present) Teri Billings (WC VI-Present) Zach Lytle (BB FaceOffs 2024)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Horizontal bar spinner</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Perfect Phoenix (Terri Billings, Tyler Nguyen) Malice (Ray Billings) Jet Lag , B.O.B. , Son of Bob , Low Blow , Deathstar , Mow-Blow , Mr. "D" , Final Verdict , Hellfire (Rick Russ) Skorpios (Zach Lytle)</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>8S 5.8Ah LiPo battery</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Darkness , The Raven , Swamp Thing , The Mortician</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Pro Championship 2009</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tracer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>World Championship V World Championship VI (Not selected)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Team KYMERA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Jason Woods (Captain) Adam Majewski Danny Jimenez Jack Ring Justin Bitagon</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Sacramento &amp; McKinney, TX Gold River, CA</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Slingshot , Rebob , JackPot (Jason Woods)</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>12-13S 20Ah LiPo batteries</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Uppercut</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>World Championship IV World Championship V World Championship VI</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BattleBots: Champions I</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Team Uppercut (formerly MIT Combat Robotics Club)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Alex Hattori (Captain) Mason Massie Chetan Sharma Jared DiCarlo Greg Xie Jackson Gray Sofia Leon (WC IV-WC V) Devansh Agrawal (WC IV, WC VI) Dayna Erdmann (WC IV) Lili Sun (WC V) Tiffany Hattori (WC V) Linda Hattori (WC V) Austin Brown (WC V-BB: Champions I) Jonhenry Poss (WC V) Jen Curtiss (WC V) Saba Zerefa (WC V) Sam Ferguson (WC V) Jules Ferguson (WC VI) Aaron Sliski (WC VI) Anna Zolnikov (WC VI-BB: Champions I) Jeremy Germita (WC VI) Amy Fang (WC IV) Sarah Pohorecky (WC IV)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SawBlaze (Alex Hattori) Road Rash (Jared DiCarlo, Alex Hattori) P1 (Sarah Pohorecky) Starchild , Ripperoni (Anna Zolnikov, Sarah Pohorecky, Austin Brown) The Dentist (Austin Brown) LOLcano , Deathicator (Austin Brown, Anna Zolnikov)</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Valkyrie</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Team VALKYRIE (WC VI-Present) Team Questionable Designs (WC III-WC V)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Leanne Cushing (Captain) Lucy Du (WC VII-BB: Champions II) Frederick Moore (WC III-BB: Champions I) Alex Crease Brooks Willis (WC III-WC IV) Amanda Fowler (WC IV-BB: Champions I) Ryan Brown (WC IV) Fangzhou Yu (WC IV) Lucas Ewing (WC V-BB: Champions I) Daniel Gonzalez (WC VI-BB: Champions I) Bradley Roan (WC VI-BB: Champions I) Morgan Locandro (WC VII-BB: Champions II) John Mayo (WC VII-Present) Bam Singhasaneh (WC VII-Present) George Tan (WC VII-Present) Regan Tattersfield (WC VII-BB: Champions II) Esme Abbot (WC VII-Present) Jason Vasquez (BB Pro League 2026) Peter Schmehl (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Berkeley, CA (BB FaceOffs-Present) Somerville, MA (WC IV-BB: Champions II) Cambridge, MA (WC III)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Undercutter spinner</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>SawBlaze (Lucy Du, John Mayo) , RIPperoni , Starchild , Road Rash (Frederick Moore) Overhaul (Lucy Du) Whiplash , Defender , Splatter , Think Tank (Jason Vasquez)</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Whiplash</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2x Mini Magmotors (WC IV-Present) 2x 48v AmpFlow motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>250lbs</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Team Fast Electric Robots</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Matt Vasquez (Captain) Jason Vasquez Jeff Vasquez Debbie Vasquez Daisy Gonzalez (WC VI-Present)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Lifter Vertical spinner</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>VD6.0 (Jeff Vasquez) Manta (Matt Vasquez)</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Deb Bot , Matts Bammer , Think Tank , Splatter , Defender</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Witch Doctor</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>250lbs (WC I-Present) 120lbs (BotsIQ 2010-BotsIQ 2011)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>World Championship I World Championship II World Championship III World Championship IV World Championship V World Championship VI World Championship VII</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Champions I BattleBots Pro League (2026)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Team Witch Doctor (formerly Busted Nuts Robotics)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Andrea Gellatly (Captain) Mike Gellatly (Captain) Paul Grata Jennifer Villa (WC I-WC IV) Brian Lepley (WC II) Carolina de Freitas (WC II) Christian Chiriboga (WC III-Present) Steven Sharp (WC III-Present) Katheryn Sharp (WC III-Present) Rick Pease (WC IV-Present) Andrew Rudolph (WC VI-Present) Kurtis Wanner (WC VI-Present) Brett Heininger (WC VII-Present) Adam Bercu (BotsIQ 2010-BotsIQ 2011)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Miami, FL</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Vertical disk spinner Vertical drisk spinner (WC II-Present) Flamethrower</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Lucky , Hack &amp; Slash (Kurtis Wanner) Mohawk (Christian Chiriboga) Coincidence , Brutus , Overhaul (Adam Bercu) Safety Factor , Category 5 (Andrea Suarez, Mike Gellatly) The Kerminator , Marvinator , Commander K-9 (Andrea Gellatly, Carolina de Freitas) UM Spin EM (Andrea Suarez)</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>BattleBots FaceOffs (2024)</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>BotsIQ 2010 BotsIQ 2011</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/battlebots_2015_2025.xlsx
+++ b/battlebots_2015_2025.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 11 (2021)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 12 (2022)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Features" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Correlations" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20002,7 +20003,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20043,13 +20043,6 @@
           <t>Flipper</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20057,8 +20050,6 @@
           <t>Axe Backwards</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20074,7 +20065,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Team Axe Backwards (formerly KurTrox Robotix)</t>
@@ -20095,13 +20085,6 @@
           <t>Full body drum spinner</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20114,7 +20097,6 @@
           <t>2x Long Magmotors</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>235lbs</t>
@@ -20165,11 +20147,6 @@
           <t>6x MaxAmps 3S LiPo batteries</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20182,7 +20159,6 @@
           <t>2x Long Magmotors</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>227lbs (WC III) [ 1 ]</t>
@@ -20198,7 +20174,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Forge &amp; Farm Combat Robots</t>
@@ -20224,12 +20199,6 @@
           <t>Blacksmith (Kyle Singer, Earl Pancoast III) Red Devil (Earl Pancoast III) Animosity (Alex Grant) The Executioner , Roadkill (Miro Matheson)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20242,7 +20211,6 @@
           <t>4x Flipsky 6384 brushless motors</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20258,7 +20226,6 @@
           <t>BattleBots: Champions II BattleBots Pro League (2026) (Alternate)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Team Small Robots</t>
@@ -20294,10 +20261,6 @@
           <t>BattleBots Proving Ground (2023) BattleBots Proving Ground (2024) BattleBots FaceOffs (2025)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -20305,8 +20268,6 @@
           <t>Basilisk</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>245lbs</t>
@@ -20317,8 +20278,6 @@
           <t>World Championship II World Championship III</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>MBS Robotics</t>
@@ -20339,13 +20298,6 @@
           <t>Flipper Pneumatic spike (WC II) Flamethrower (WC III)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20358,14 +20310,11 @@
           <t>2x Electric scooter motors</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>World Championship III</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Bacon Double Slamburger (Working name)</t>
@@ -20401,15 +20350,11 @@
           <t>8S LiPo batteries</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>Gloomweaver , Fowl Play</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20417,8 +20362,6 @@
           <t>BattleSaw</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20429,8 +20372,6 @@
           <t>World Championship II (Not selected) World Championship III (Withdrew) World Championship IV World Championship V (Withdrew)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Twister Robotics</t>
@@ -20456,12 +20397,6 @@
           <t>Gamma 9 , Namreko 3000 , Gammatron , Gammacide (Curtis Nemeth) Bellator , Swamp Thing (Mark Elam)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20474,7 +20409,6 @@
           <t>2x Maytech 6880 brushless motors (WC VII-Present) 2x 48v Bosch DC motors (WC I-BB: Bounty Hunters) 2x 36V Magmotor S28-200 motors (Season 5.0)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>250lbs (WC I-Present) 219lbs (Season 5.0)</t>
@@ -20525,7 +20459,6 @@
           <t>12S LiPo batteries 3Ah NiCad BattlePacks (Season 5.0)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>KillerHurtz , TerrorHurtz</t>
@@ -20536,8 +20469,6 @@
           <t>Season 5.0 (Withdrew)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20550,7 +20481,6 @@
           <t>4x Maytech 6374 brushless motors</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20596,16 +20526,11 @@
           <t>WAR Hawk , Jäger (Emmanuel Carrillo, Andy Russell) Overhaul (Elizabeth Cao) Horizon (Tommy Wong) MadCatter (Emmanuel Carrillo, Ryan Lau) Malice (Isaak Malers) Chronos (Trent Wilson) Dark Steel , Dark Shredder , Dome of Darkness (Russ Barrow) Goblin (Ellis Ware)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20618,7 +20543,6 @@
           <t>2x S28-400 Magmotors (9hp) [ 2 ]</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20669,15 +20593,11 @@
           <t>10x 5Ah 6S Turnigy Nano-tech LiPo batteries (WC II-WC III) [ 1 ]</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>Brutality , Green Wave , Tantrum , Ntertainment , Land Shark , Knockturnal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20690,7 +20610,6 @@
           <t>2x 8025 Brushless motors (WCVIII-Present) 2x Magmotors (WC IV-BB: Champions II)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20706,7 +20625,6 @@
           <t>BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Team Uai!rrior</t>
@@ -20727,13 +20645,6 @@
           <t>Eggbeater drum spinner Flamethrower</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20741,9 +20652,6 @@
           <t>Black Widow</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>World Championship V</t>
@@ -20754,7 +20662,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Team Black Widow</t>
@@ -20775,13 +20682,6 @@
           <t>Drum spinner Flamethrower</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20789,8 +20689,6 @@
           <t>Blacksmith</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20806,7 +20704,6 @@
           <t>BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Team Half Fast Astronaut</t>
@@ -20832,12 +20729,6 @@
           <t>Bale Spear (Earl Pancoast III, Kyle Singer) Golem , Scuttle (James Iocca)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20850,7 +20741,6 @@
           <t>2x TP5680 brushless motors</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -20896,16 +20786,11 @@
           <t>Insult and Injury (Aren Hill, Jason Weihman, Bryan Culver)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Tantrum , The Twins</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20918,7 +20803,6 @@
           <t>4x Brushless TP Motors</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>247-250lbs</t>
@@ -20979,9 +20863,6 @@
           <t>Retrograde , Subatomic , Fireball</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20994,7 +20875,6 @@
           <t>4x Magmotors</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>245-250lbs</t>
@@ -21005,8 +20885,6 @@
           <t>World Championship II World Championship III World Championship IV</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Chaos Corps</t>
@@ -21037,11 +20915,6 @@
           <t>8s 10Ah LiPo battery</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21054,7 +20927,6 @@
           <t>4x Magmotors</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>140lbs (Cisco Party 2006) 220lbs (2009, WC IV)</t>
@@ -21070,7 +20942,6 @@
           <t>Cisco Party 2006</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Team Nightmare</t>
@@ -21091,25 +20962,21 @@
           <t>Lifting scoop Hammer (WC IV)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>MaxAmps LiPo batteries</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Rhino , Junior , Nightmare , Backlash , Whirligig , Turtle , ShazBot , MicroNightmare , Wallop , Grasshopper , The Swarm ( Locust )</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>Pro Championship 2009</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21122,7 +20989,6 @@
           <t>6x 3" Brushed motors (WC II) 4x motors (WC I, WC III-Present)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21138,7 +21004,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Destruct-A-Thon</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>Inertia Labs</t>
@@ -21159,21 +21024,16 @@
           <t>Flipping arm</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>LiFePO batteries (Destruct-A-Thon)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>Toro , The Matador , T-Minus , Rhino , The Butcher</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21186,7 +21046,6 @@
           <t>2x Brushless motors (WC III) 2x NPC brushed motors (WC II)</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>242lbs</t>
@@ -21197,8 +21056,6 @@
           <t>World Championship II World Championship III</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Team Brutus</t>
@@ -21224,12 +21081,6 @@
           <t>Overhaul , Witch Doctor , Coincidence (Adam Bercu) Valkyrie , RIPperoni , Starchild (Amanda Fowler)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -21237,8 +21088,6 @@
           <t>Captain Shrederator</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>220lbs [ 1 ]</t>
@@ -21284,16 +21133,11 @@
           <t>Lucky (Zac O'Donnell) Raven , Ultimo Destructo , Purple Fire (Jacob Rogers) Skorpios , Malice (Jonathan LaPlain) Triton , Deep Six , Bad Kitty , Switchback , Chronos , VD6.0 (Bradley Hanstad)</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Chopper , Code:BLACK , Dispose-All , Phrizbee , Phrizbee-Ultimate , Shredhead , Pincer</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21301,8 +21145,6 @@
           <t>Chomp</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>250lbs (WC I-re:MARS 2019) 500lbs (WC V-BB: Bounty Hunters)</t>
@@ -21318,7 +21160,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>The Machine Corps</t>
@@ -21344,12 +21185,6 @@
           <t>The Judge , The Prosecutor , Juggernaut (Jascha Little)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21357,8 +21192,6 @@
           <t>Chronos</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>243lbs</t>
@@ -21374,7 +21207,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Team Chronos</t>
@@ -21405,15 +21237,11 @@
           <t>MaxAmps LiPo batteries</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>No Luv , El Cucuy</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -21426,7 +21254,6 @@
           <t>4x RV-120E brushless motors</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>250lbs ~238lbs (WC V) [ 1 ]</t>
@@ -21472,16 +21299,11 @@
           <t>WAR Hawk (Kevin Milczewski, Joshua Beavers)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>BattleBots Proving Ground BattleBots FaceOffs (2024)</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -21494,8 +21316,6 @@
           <t>2x HyperDrive motors</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>World Championship II World Championship IV World Championship V (Withdrew) World Championship VI World Championship VII</t>
@@ -21506,7 +21326,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions II BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Robotic Death Company (WC VI-Present) Team Carbide (WC II, WC IV)</t>
@@ -21532,7 +21351,6 @@
           <t>Axolotl , Horizon (Alon Belkin) Wrecks , Skorpios , Tiki Fire (Micah Leibowitz) Stinger: The Killer Bee , Devil's Plunger , Sewer Snake , Wipe Out #2 (Matt Maxham, Wendy Maxham) Quantum (James Cooper) Beta (Dave Moulds) Taco Tuesday (Camden Wallraff) Lucky (Matt Olson, Mark Demers) Calypso (Alon Belkin, Derek Tran, Alex Price) Manta , Golden Fury (Derek Tran) JackPot (Derek Tran, David Le) Banshee (Alon Belkin, Alex Price) Nemesis (David Le) Ziggy , CycloneBot , PitBot , BravePart (Mark Demers)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs (2024)</t>
@@ -21543,9 +21361,6 @@
           <t>Gigabyte , Megabyte , Rambite , Invader , Super Megabyte , Agsma</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -21558,7 +21373,6 @@
           <t>2x Maytech MTO6365 motors (BB Pro League 2026)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21609,15 +21423,11 @@
           <t>5Ah 6S LiPo batteries</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>Poison Arrow</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -21630,7 +21440,6 @@
           <t>4x Maytech 65162 brushless motors</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21681,15 +21490,11 @@
           <t>4x MaxAmps 4Ah 37V 150C LiPo batteries</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>The Ringmaster , Marvin</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -21702,14 +21507,11 @@
           <t>2x Custom motors</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>World Championship IV</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Daisycutter</t>
@@ -21735,17 +21537,11 @@
           <t>Vertical spinning disks</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -21758,7 +21554,6 @@
           <t>T-MOTOR P80III KV100 motors</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21774,7 +21569,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>RoboGym Robotics</t>
@@ -21795,17 +21589,11 @@
           <t>Lifter Grappler (WC VI-BB: Champions I) Flamethrower</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>Roundhouse , Snatch</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -21813,8 +21601,6 @@
           <t>DeathRoll</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>243-250lbs</t>
@@ -21855,17 +21641,11 @@
           <t>Vertical spinning disk</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>48V LiPo battery system</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21878,7 +21658,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21894,7 +21673,6 @@
           <t>BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>Team Overboard</t>
@@ -21925,15 +21703,11 @@
           <t>3.4Ah 6S LiPo batteries</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>Triton</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -21946,7 +21720,6 @@
           <t>4x Magmotors</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -21962,7 +21735,6 @@
           <t>BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Team Fast Electric Robots</t>
@@ -21988,16 +21760,11 @@
           <t>Bite Force , Lucky , Scrap Metal , FrostBite (Rob Masek) Manta (Matt Vasquez) Valkyrie (Jason Vasquez) VD6.0 (Jeff Vasquez)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>Whiplash , Splatter , Deb Bot , Matts Bammer , Think Tank</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -22005,8 +21772,6 @@
           <t>Deviled Egg</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22017,8 +21782,6 @@
           <t>World Championship III World Championship VI (Not selected)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>Recoil Robotics</t>
@@ -22044,12 +21807,6 @@
           <t>Sharko , Riptide (Zak Hassanein) Mega Tento (Ryan Hasty) Clockwork L'Orange (Shannon &amp; Kathy O'Hare)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -22057,12 +21814,6 @@
           <t>Doom</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>Team Bad Bot</t>
@@ -22083,17 +21834,11 @@
           <t>Hinged wedge</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>NPC Charity Open</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22106,7 +21851,6 @@
           <t>2x Surpass 70120 brushless motors</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22117,7 +21861,6 @@
           <t>World Championship VII (Alternate)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Dooomba</t>
@@ -22148,12 +21891,6 @@
           <t>Battle Royale With Cheese (Brice Farrell) Mammoth (Thuong Nguyen, Brice Farrell, Liz Chavarria) Sporkinok (Liz Chavarria) Pardon My French (Philippe Voyer)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -22166,7 +21903,6 @@
           <t>4x Long Magmotors</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>248½lbs</t>
@@ -22177,8 +21913,6 @@
           <t>World Championship II (Withdrew) World Championship III</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>Iron LungFish Robotics</t>
@@ -22199,17 +21933,11 @@
           <t>Twin horizontal bar spinners</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>Chomp . Mongus , Spwack</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -22222,7 +21950,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>248lbs</t>
@@ -22263,17 +21990,11 @@
           <t>Cannon</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>8Ah 25C LiPo battery</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -22281,8 +22002,6 @@
           <t>Double Tap</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22293,7 +22012,6 @@
           <t>World Championship VII (Alternate) BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>DoubleTap</t>
@@ -22319,13 +22037,6 @@
           <t>Adjustable angled blade with centrifical hammers</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -22333,16 +22044,11 @@
           <t>Dragon King</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>World Championship VII (Alternate)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>Bots Bash Party Crew</t>
@@ -22368,7 +22074,6 @@
           <t>Slap 'Em Silly Slap 'Em Sillier Sledge-Jammer (Andy Sauro) Tombstone (Zach Lytle)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>BattleBots Proving Ground (2026)</t>
@@ -22379,9 +22084,6 @@
           <t>Skorpios</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -22394,7 +22096,6 @@
           <t>2x Long Magmotors (WC VII-Present) 2x NPC-T64 motors (WC VI)</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>225-250lbs</t>
@@ -22445,15 +22146,11 @@
           <t>2x Spektrum 5Ah 100c 4S LiPo batteries (vs. Minotaur) MaxAmps 9000XL 6S LiPo batteries (vs. DUCK!) 2x GensAce 7.5Ah 100c 4S LiPo batteries (vs. Blade and Uppercut) [ 2 ]</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>Piranha</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -22461,16 +22158,11 @@
           <t>Electric Ray</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>World Championship IV (Withdrew)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>Team Robot Revolution</t>
@@ -22496,12 +22188,6 @@
           <t>Ribbot (Lucas Buermeyer)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22514,7 +22200,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22530,7 +22215,6 @@
           <t>BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Bots FC</t>
@@ -22551,17 +22235,11 @@
           <t>Vertical spinner</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>Shatter! Bliss 2 Doomba and Friends</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -22574,7 +22252,6 @@
           <t>4x 6374-192kV Motors</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22625,15 +22302,11 @@
           <t>2x 1.8Ah MaxAmps batteries</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>Krusty Grab</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -22646,7 +22319,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22662,7 +22334,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Quicksilver Robotics</t>
@@ -22688,12 +22359,6 @@
           <t>Gruff (John Flaacke IV)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -22706,7 +22371,6 @@
           <t>2x Magmotors (NPC Charity Open-2009 Collegiate Championship)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>250lbs (WC IV) 120lbs (NPC Charity Open-2009 Collegiate Championship)</t>
@@ -22717,7 +22381,6 @@
           <t>World Championship I (Not selected) World Championship IV</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Falconizer (NPC Charity Open)</t>
@@ -22743,7 +22406,6 @@
           <t>Twin drum spinners (WC IV) Single drum spinner (NPC Charity Open-2009 Collegiate Championship)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>MaxAmps LiPo batteries</t>
@@ -22759,7 +22421,6 @@
           <t>Hydra , Fusion , Red Square , Son of Whyachi , Warrior , Warrior Clan , Whyachi , Why Not , Y-Pout , YU812 , Falcon15 , Buzzkill</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>Collegiate Championship 2009</t>
@@ -22782,7 +22443,6 @@
           <t>4x TD6374 Motors</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>203lbs</t>
@@ -22793,8 +22453,6 @@
           <t>World Championship IV</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>Team Danby</t>
@@ -22825,15 +22483,11 @@
           <t>4.5Ah 25C Nanotech LiPo batteries</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Predator , Slammo! , Apex</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22841,8 +22495,6 @@
           <t>Free Shipping</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>250lbs (WC III-WC VI) 210lbs (WC VII-Present) [ 1 ]</t>
@@ -22858,7 +22510,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>Team Special Delivery</t>
@@ -22884,7 +22535,6 @@
           <t>Voltronic , The Swarm (Stephen Felk) Lucky , Wipe Out #2 (Gary Gin) Yeti (James Arluck, Ange Santaguida) VD6.0 , Wrecks , Shockwave (James Arluck) Robo Master (Jim Yeh, Forrest Yeh) Agent X (Jim Yeh)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs</t>
@@ -22895,9 +22545,6 @@
           <t>The Big B</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22910,7 +22557,6 @@
           <t>Brushless motors</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -22926,7 +22572,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Team Whyachi</t>
@@ -22957,15 +22602,11 @@
           <t>18x 4S LiPo batteries</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>Hydra , Son of Whyachi , Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Warrior Clan , Falcon , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22973,9 +22614,6 @@
           <t>GRABOT</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>World Championship V</t>
@@ -23011,13 +22649,6 @@
           <t>Grabbing arms Wedge</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23025,8 +22656,6 @@
           <t>Gamma 9</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23037,7 +22666,6 @@
           <t>World Championship III World Championship V</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Gamma 9 from Outer Space (WC V)</t>
@@ -23068,16 +22696,11 @@
           <t>BattleSaw (Curtis Nemeth)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>Namreko 3000 , Gammatron , Gammacide</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23090,7 +22713,6 @@
           <t>4x AmpFlow motors (2x per half)</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>250lbs (125lbs each)</t>
@@ -23136,12 +22758,6 @@
           <t>Slap Box (Dominic &amp; Hunter Yankauskas) Bolt , MacGuffin , ZAP (Ben Hayton)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -23154,7 +22770,6 @@
           <t>2x A28-150 AmpFlow motors</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>248lbs</t>
@@ -23170,7 +22785,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Team Raptor</t>
@@ -23201,15 +22815,11 @@
           <t>8S 5Ah batteries</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>Alpha Raptor , Tripulta Raptor , Pack Raptors , Carnage Raptor , W.L.O.W.</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -23222,7 +22832,6 @@
           <t>2x TP5680 brushless motors (WC VII-Present) 2x Short Magmotors (WC III-WC VI)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23238,7 +22847,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Robotic Death Company</t>
@@ -23279,9 +22887,6 @@
           <t>Megabyte , Rambite , Invader , Cobalt , Super Megabyte , Agsma</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -23294,7 +22899,6 @@
           <t>4x Scorpion SII-4035-450KV motors</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23310,7 +22914,6 @@
           <t>BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Combat Robotics at Berkeley</t>
@@ -23341,15 +22944,11 @@
           <t>10S 6.5Ah LiPo battery (WC VII-BB: Champions II) 8S 8Ah LiPo battery (WC VI-BB: Champions I)</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Holy CR@B , Thunderstorm</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -23362,7 +22961,6 @@
           <t>4x Ampflow E30-400 brushed motors (WC IV)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23408,12 +23006,6 @@
           <t>Quasar (Sam McAmis) Extinguisher (John Flaacke IV) Slammo! (Jason Rogers)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23426,7 +23018,6 @@
           <t>2x Maytech 8085 brushless motors</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23442,7 +23033,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Team HUGE</t>
@@ -23473,11 +23063,6 @@
           <t>12x 6S 2.8Ah LiPo batteries [ 1 ]</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -23490,7 +23075,6 @@
           <t>2x Castle 1515 brushless motors</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>242-250lbs</t>
@@ -23551,9 +23135,6 @@
           <t>Skorpios</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -23566,7 +23147,6 @@
           <t>2x TP5680 Brushless inrunner motors</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>225lbs</t>
@@ -23627,9 +23207,6 @@
           <t>Calypso</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -23642,7 +23219,6 @@
           <t>4x Brushless motors</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -23703,9 +23279,6 @@
           <t>Son of Whyachi , Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Warrior Clan , Fusion , Falcon , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23718,7 +23291,6 @@
           <t>2x NeuMotor 8038 motors</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>238-250lbs</t>
@@ -23779,9 +23351,6 @@
           <t>Hot Mess , Vertigo</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -23794,7 +23363,6 @@
           <t>2x AmpFlow 48V motors</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>231½-248lbs</t>
@@ -23805,8 +23373,6 @@
           <t>World Championship III</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Team Toad</t>
@@ -23837,15 +23403,11 @@
           <t>MaxAmps 36V LiPo batteries</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>Texas Twister , El Furro , Ice Chip , TadPole , SnowCone , WindChill , IceCube , SnowFlake , IceBerg , FrostBite</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -23858,7 +23420,6 @@
           <t>2x Magmotors</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>250lbs (WC I-Present) 120lbs (2004-2007)</t>
@@ -23909,15 +23470,11 @@
           <t>2x 6S 5Ah LiPo batteries</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>Edge , Vault</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -23925,8 +23482,6 @@
           <t>JackPot</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>243-250lbs</t>
@@ -23982,10 +23537,6 @@
           <t>BattleBots Proving Ground (2023) BattleBots FaceOffs (2024) BattleBots Proving Ground (2025) BattleBots FaceOffs (2025)</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -23998,15 +23549,11 @@
           <t>4x Ampflow A28-400 brushed motors [ 1 ] [ 2 ]</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>World Championship IV</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Tomco Designs</t>
@@ -24032,12 +23579,6 @@
           <t>Radioactive , X/Change (Kevin Cleasby)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -24045,8 +23586,6 @@
           <t>Jäger</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>246lbs (Combined)</t>
@@ -24057,7 +23596,6 @@
           <t>World Championship V (Withdrew) World Championship VI World Championship VII (Not selected)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>Jager</t>
@@ -24088,12 +23626,6 @@
           <t>Nelly the Ellybot (Charlie Dangerfield) Big Dill (Andy Russell, Emmanuel Carrillo) Abrasion (Ed Hodges)</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -24106,7 +23638,6 @@
           <t>2x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24117,8 +23648,6 @@
           <t>World Championship IV World Championship V (Withdrew) World Championship VI (Not selected)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Team Burntpopcorn</t>
@@ -24139,13 +23668,6 @@
           <t>Horizontal bar spinner</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -24158,7 +23680,6 @@
           <t>4x HyperDrive motors (WC VII-Present) 2x NPC-T74 motors (WC III-BB: Champions I)</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>249lbs</t>
@@ -24199,13 +23720,6 @@
           <t>Crusher Articulating vertical spinner (WC VII-Present)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -24218,7 +23732,6 @@
           <t>4x Ampflow-A28-250 motors</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24269,15 +23782,11 @@
           <t>17Ah LiFePO batteries (6-8S)</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>CU-JAW , Diesector , Tazbot , Easty Beast , Root Canal , Gear Crow</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -24290,7 +23799,6 @@
           <t>2x Magmotors</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24336,7 +23844,6 @@
           <t>Free Shipping , The Big B , Wipe Out #2 (Gary Gin) Captain Shrederator (Zac O'Donnell) Defender , Bite Force , FrostBite , Scrap Metal (Rob Masek) Deep Six , Triton , Malice (Andrew Burghgraef) Witch Doctor , Hack &amp; Slash (Kurtis Wanner) BravePart , PitBot (Mark Demers, Jeff Hayashida, Mohan Gurunathan, Robert Frankovich, Jerome Johnson) Cobalt (Matt Olson, Mark Demers) Nerd Killer , Shockwave , VD6.0 , Wrecks , Yeti (James Arluck)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>BattleBots Proving Ground BattleBots FaceOffs</t>
@@ -24347,9 +23854,6 @@
           <t>Ziggy , CycloneBot</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -24362,7 +23866,6 @@
           <t>6x 9kW Brushless motors</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24423,9 +23926,6 @@
           <t>Bad Kitty , CatKong</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -24438,7 +23938,6 @@
           <t>2x S28-D4-400x Long Magmotors</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24454,7 +23953,6 @@
           <t>BattleBots: Bounty Hunters re:MARS all:STARS (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Team Malice</t>
@@ -24480,16 +23978,11 @@
           <t>Wrecks , Shatter! (Adrian "Bunny" Liaw) Silver Shield (David Liaw) Big Dill (Isaak Malers) Banshee (David Small, David Rush) Drago (Nick Dobrikov) Skorpios (Adrian "Bunny" Liaw, David Liaw, Jonathan LaPlain) Doomba and Friends (Adrian "Bunny" Liaw) Tombstone , Swamp Thing , Darkness , The Raven , Skorpios (Ray Billings) Captain Shrederator (Jonathan LaPlain) Horizon (Peter Garnache) VD6.0 (Alex Tramiel) JackPot (Scott Johnston)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs (2024)</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -24502,7 +23995,6 @@
           <t>2x RV-100 motors</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24518,7 +24010,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Team Mammoth</t>
@@ -24549,11 +24040,6 @@
           <t>MaxAmps LiPo batteries</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -24561,8 +24047,6 @@
           <t>Mecha Rampage</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24573,8 +24057,6 @@
           <t>World Championship III</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>C2 Robotics (formerly Team Coolrobots)</t>
@@ -24600,16 +24082,11 @@
           <t>Yeti , Chunk (Christian Carlberg)</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>OverDrive , Minion , OverKill , Toe-Crusher , Dreadnought , Knee-Breaker , UpperCut , TriDent , Nasty , Little Killer</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24622,7 +24099,6 @@
           <t>4x Maytech 6374 brushless motors</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>250lbs (WC IV-WC V) 235lbs (WC VI)</t>
@@ -24668,16 +24144,11 @@
           <t>Uppercut (Sarah Pohorecky) Starchild , RIPperoni (Brandon Zalinsky, Sarah Pohorecky)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>Parallax , Talos</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24685,8 +24156,6 @@
           <t>Pain Train</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24702,7 +24171,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Team Shreddit</t>
@@ -24733,15 +24201,11 @@
           <t>3x 5Ah 45C LiPo batteries</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>SHREDDIT BRO!</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24754,7 +24218,6 @@
           <t>2x Long Magmotors</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>169-230lbs</t>
@@ -24770,7 +24233,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Team Doom Robotics</t>
@@ -24796,12 +24258,6 @@
           <t>Tombstone , Malice (Ray Billings) Brutality (Alternative identity)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24814,7 +24270,6 @@
           <t>4x AmpFlow E30-400 motors</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>245lbs</t>
@@ -24830,7 +24285,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Team X</t>
@@ -24851,17 +24305,11 @@
           <t>Vertical spinner</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>4x Turnigy Nanotech 5Ah 5S LiPo batteries</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24874,7 +24322,6 @@
           <t>2x S28-150 Magmotors</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24890,7 +24337,6 @@
           <t>BattleBots: Champions I BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Team Ribbot (formerly Team WPI)</t>
@@ -24916,12 +24362,6 @@
           <t>Electric Ray (Lucas Buermeyer)</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24929,23 +24369,6 @@
           <t>Rotator</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24953,8 +24376,6 @@
           <t>Rusty</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -24995,17 +24416,11 @@
           <t>Jackhammer Sledgehammer Lifter</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs (2024)</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -25013,23 +24428,6 @@
           <t>SMEEEEEEEEEEE</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -25042,7 +24440,6 @@
           <t>2x T&amp;P brushless motors 2x Black Max motors (WC III)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25098,10 +24495,6 @@
           <t>BattleBots: Destruct-A-Thon</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -25114,7 +24507,6 @@
           <t>2x MC160 motors</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>220lbs</t>
@@ -25160,16 +24552,11 @@
           <t>Deviled Egg , Riptide (Zak Hassanein) P.T. Bruiser , Robot X (Edward Robinson)</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>Mantasaur , TriloBot</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -25182,7 +24569,6 @@
           <t>4x Castle 2028 brushless motors</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25233,15 +24619,11 @@
           <t>MaxAmps LiPo batteries</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>Emulsifier Doomba and Friends Bliss 2</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -25254,7 +24636,6 @@
           <t>2x Long Magmotors (WC II - WC IV) 4x Short Magmotors (WC V-BB: Champions II) 2x Long Magmotors &amp; 2x Small Magmotors (WCVIII-Present)</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>~250lbs</t>
@@ -25270,7 +24651,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>Bot Bash Party Crew (formerly Offbeat Robotics )</t>
@@ -25311,9 +24691,6 @@
           <t>Dragon King</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -25321,23 +24698,6 @@
           <t>SlamMow!</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -25345,8 +24705,6 @@
           <t>Slap Box</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25392,12 +24750,6 @@
           <t>Gemini (Dominic Yankauskas, Hunter Yankauskas)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -25410,7 +24762,6 @@
           <t>4x Astro 90 Cobalt motors</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>250lbs (WC I-Present) 315lbs (Season 3.0-5.0)</t>
@@ -25461,7 +24812,6 @@
           <t>Various 4S and 5S LiPo batteries</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>Whyachi , YU812 , Y-Pout , Why Not , Red Square , Warrior , Hydra , Fusion , Falcon , Warrior Clan , Warrior SKF , Falcon15 , 1A , 3A . POW , BABS , Ricochet , Buzzkill</t>
@@ -25472,8 +24822,6 @@
           <t>Season 3.0 Season 4.0 Season 5.0</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -25486,7 +24834,6 @@
           <t>4x 6474 Brushless motors</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25502,7 +24849,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>Team PRIDE</t>
@@ -25528,12 +24874,6 @@
           <t>Doomba (Liz Chavarria)</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -25541,8 +24881,6 @@
           <t>SubZero</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>250lbs (WC II-Present) 220lbs (2009 Pro Championship) 140lbs (NPC Charity Open-JavaOne 2007)</t>
@@ -25588,7 +24926,6 @@
           <t>Lock-Jaw (Reginald Wilson, Logan Davis, Brady Davis) The Cone Army , Mixmaster (Alex Horne) Texas Twister (Brady Davis) Mudhole Bullfrog , Total Anarchy (Jon Durand) Switchback (Logan Davis)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>2004 NPC Charity Open R3: Rochester Robot Rampage BattleBots JavaOne 2007</t>
@@ -25599,13 +24936,11 @@
           <t>Team Hammertime Hammertime , Bounty Hunter Team XD Steel Reign , HazMatXD , Adonai , RobotussinDM , ...Tysant</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr">
         <is>
           <t>Pro Championship 2009</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -25618,7 +24953,6 @@
           <t>2x TP5680 brushless motors</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>250lbs (WC IV-Present) 235lbs (WC III)</t>
@@ -25634,7 +24968,6 @@
           <t>BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>Seems Reasonable Robotics</t>
@@ -25665,15 +24998,11 @@
           <t>4x 5.4Ah 6S LiPo batteries</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>Blip , The Twins</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -25686,7 +25015,6 @@
           <t>Various Ranglebox motors</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>~250lb combined</t>
@@ -25697,7 +25025,6 @@
           <t>World Championship III World Championship IV</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>Four Horsemen</t>
@@ -25723,21 +25050,16 @@
           <t>Various horizontal spinners</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>5S LiPo batteries</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>Creepy Crawlies , Bull Dog , Little Sister</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -25750,7 +25072,6 @@
           <t>2x Maytech 8085 brushless outrunners</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>220lbs (Pro Championship 2009) 250lbs (WC I-Present) 340lbs (NPC Charity Open)</t>
@@ -25766,7 +25087,6 @@
           <t>2004 NPC Charity Open re:MARS all:STARS (2019) BattleBots: Bounty Hunters re:MARS all:STARS (2022) BattleBots: Champions I BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Hardcore Robotics</t>
@@ -25777,7 +25097,6 @@
           <t>Ray Billings (Captain) Rick Russ (WC I-BB: Champions I) Justin Billings Brittney Billings (WC II, WC VI-Present) Lorna West (WC V-BB: Champions I) Susan Billings (WC II) Roy Hellen (WC V-BB: Bounty Hunters) Tyler Nguyen (WC V-BB: Champions I) Kevin Benesi (WC VI-Present) Teri Billings (WC VI-Present) Zach Lytle (BB FaceOffs 2024)</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>Horizontal bar spinner</t>
@@ -25803,13 +25122,11 @@
           <t>Darkness , The Raven , Swamp Thing , The Mortician</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
           <t>Pro Championship 2009</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -25817,8 +25134,6 @@
           <t>Tracer</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25834,7 +25149,6 @@
           <t>BattleBots: Bounty Hunters</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>Team KYMERA</t>
@@ -25865,11 +25179,6 @@
           <t>12-13S 20Ah LiPo batteries</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -25877,8 +25186,6 @@
           <t>Uppercut</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25894,7 +25201,6 @@
           <t>BattleBots: Champions I</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>Team Uppercut (formerly MIT Combat Robotics Club)</t>
@@ -25920,12 +25226,6 @@
           <t>SawBlaze (Alex Hattori) Road Rash (Jared DiCarlo, Alex Hattori) P1 (Sarah Pohorecky) Starchild , Ripperoni (Anna Zolnikov, Sarah Pohorecky, Austin Brown) The Dentist (Austin Brown) LOLcano , Deathicator (Austin Brown, Anna Zolnikov)</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -25933,8 +25233,6 @@
           <t>Valkyrie</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -25950,7 +25248,6 @@
           <t>BattleBots: Bounty Hunters BattleBots: Champions I BattleBots: Champions II BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>Team VALKYRIE (WC VI-Present) Team Questionable Designs (WC III-WC V)</t>
@@ -25976,16 +25273,11 @@
           <t>SawBlaze (Lucy Du, John Mayo) , RIPperoni , Starchild , Road Rash (Frederick Moore) Overhaul (Lucy Du) Whiplash , Defender , Splatter , Think Tank (Jason Vasquez)</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs (2024)</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25998,7 +25290,6 @@
           <t>2x Mini Magmotors (WC IV-Present) 2x 48v AmpFlow motors (WC III)</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>250lbs</t>
@@ -26014,7 +25305,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) re:MARS all:STARS BattleBots Challenge (2022) BattleBots: Champions I BattleBots: Champions II</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>Team Fast Electric Robots</t>
@@ -26040,16 +25330,11 @@
           <t>VD6.0 (Jeff Vasquez) Manta (Matt Vasquez)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>Deb Bot , Matts Bammer , Think Tank , Splatter , Defender</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -26062,7 +25347,6 @@
           <t>2x Long Magmotors</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>250lbs (WC I-Present) 120lbs (BotsIQ 2010-BotsIQ 2011)</t>
@@ -26078,7 +25362,6 @@
           <t>re:MARS all:STARS BattleBots Challenge (2019) BattleBots: Bounty Hunters BattleBots: Champions I BattleBots Pro League (2026)</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>Team Witch Doctor (formerly Busted Nuts Robotics)</t>
@@ -26104,19 +25387,1570 @@
           <t>Lucky , Hack &amp; Slash (Kurtis Wanner) Mohawk (Christian Chiriboga) Coincidence , Brutus , Overhaul (Adam Bercu) Safety Factor , Category 5 (Andrea Suarez, Mike Gellatly) The Kerminator , Marvinator , Commander K-9 (Andrea Gellatly, Carolina de Freitas) UM Spin EM (Andrea Suarez)</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>BattleBots FaceOffs (2024)</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>BotsIQ 2010 BotsIQ 2011</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Robot_Count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Avg_Win_Pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Overall_Avg_Win_Pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Small_Sample_Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2x S28-400 Magmotors (9hp) [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.408</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2x Maytech 6880 brushless motors (WC VII-Present) 2x 48v Bosch DC motors (WC I-BB: Bounty Hunters) 2x 36V Magmotor S28-200 motors (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6x 9kW Brushless motors</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.006</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4x Brushless motors</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.765</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2x Maytech MTO6365 motors (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4x Brushless TP Motors</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC II - WC IV) 4x Short Magmotors (WC V-BB: Champions II) 2x Long Magmotors &amp; 2x Small Magmotors (WCVIII-Present)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless motors</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2x Mini Magmotors (WC IV-Present) 2x 48v AmpFlow motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2x RV-100 motors</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2x S28-150 Magmotors</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2x S28-D4-400x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2x T&amp;P brushless motors 2x Black Max motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2x 8025 Brushless motors (WCVIII-Present) 2x Magmotors (WC IV-BB: Champions II)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4x Ampflow-A28-250 motors</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2x HyperDrive motors</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4x 6374-192kV Motors</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2x Magmotors</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2x Castle 1515 brushless motors</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4x RV-120E brushless motors</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6x 3" Brushed motors (WC II) 4x motors (WC I</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Various Ranglebox motors</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WC III-Present)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4x Maytech 6374 brushless motors</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2x NeuMotor 8038 motors</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors (WC VII-Present) 2x Short Magmotors (WC III-WC VI)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4x Scorpion SII-4035-450KV motors</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.033</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2x Brushless motors (WC III) 2x NPC brushed motors (WC II)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Brushless motors</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4x Maytech 65162 brushless motors</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4x Magmotors</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC VII-Present) 2x NPC-T64 motors (WC VI)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2x Magmotors (NPC Charity Open-2009 Collegiate Championship)</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless outrunners</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4x AmpFlow motors (2x per half)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4x Ampflow E30-400 brushed motors (WC IV)</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2x AmpFlow 48V motors</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2x TP5680 Brushless inrunner motors</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4x Flipsky 6384 brushless motors</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>T-MOTOR P80III KV100 motors</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2x A28-150 AmpFlow motors</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4x HyperDrive motors (WC VII-Present) 2x NPC-T74 motors (WC III-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2x Custom motors</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2x Electric scooter motors</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2x MC160 motors</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2x Surpass 70120 brushless motors</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4x 6474 Brushless motors</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4x Ampflow A28-400 brushed motors [ 1 ] [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4x TD6374 Motors</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>4x AmpFlow E30-400 motors</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4x Astro 90 Cobalt motors</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/battlebots_2015_2025.xlsx
+++ b/battlebots_2015_2025.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Season 12 (2022)" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weapons_BattleBotsCom" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Features" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Correlations" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40737,6 +40738,3994 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G148"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Robot_Count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Avg_Win_Pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Overall_Avg_Win_Pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lift</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Small_Sample_Warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2x S28-400 Magmotors (9hp) [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.525</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2x Short brushless Magmotors</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.259</v>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2x Maytech 6880 brushless motors (WC VII-Present) 2x 48v Bosch DC motors (WC I-BB: Bounty Hunters) 2x 36V Magmotor S28-200 motors (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless outrunners</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4x Brushless motors</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2x Maytech MTO6365 motors (BB Pro League 2026)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4x Brushless TP Motors</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.882</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4x Brushed LEM motors</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2x Mini Magmotors (WC IV-Present) 2x 48v AmpFlow motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2x Maytech 8085 brushless motors</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2x T&amp;P brushless motors 2x Black Max motors (WC III)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.718</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2x 8025 Brushless motors (WCVIII-Present) 2x Magmotors (WC IV-BB: Champions II)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4x Astro 90 Cobalt motors</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6x 9kW Brushless motors</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6x 3" Brushed motors (WC II) 4x motors (WC I</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WC III-Present)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2x 1415 Aveox 3-turn brushless DC motors</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2x S28-150 Magmotors</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2x S28-D4-400x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC II - WC IV) 4x Short Magmotors (WC V-BB: Champions II) 2x Long Magmotors &amp; 2x Small Magmotors (WCVIII-Present)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2x HyperDrive motors</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4x 6374-192kV Motors</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>4x Ampflow-A28-250 motors</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2x NPC-T64 brushed motors</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.405</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2x Magmotors</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2x Brushless motors (WC III) 2x NPC brushed motors (WC II)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2x Castle 1515 brushless motors</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2x Custom brushless motors</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2x NeuMotor 8038 motors</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2x RV-100 motors</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2x Short Magmotors (2009-WC III) 2x 12hp Briggs &amp; Stratton motors (Season 5.0) [ 1 ]</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>4x RV-120E brushless motors</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ampflow motors</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2x TP5680 brushless motors (WC VII-Present) 2x Short Magmotors (WC III-WC VI)</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4x Magmotors</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4x Scorpion SII-4035-450KV motors</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.058</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Brushless motors</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4x Maytech 6374 brushless motors</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.036</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4x Maytech 65162 brushless motors</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2x Maytech 6374 Brushless motors</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2x A28-150 AmpFlow motors</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2x Long Magmotor brushed motors</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2x Long Magmotors (WC VII-Present) 2x NPC-T64 motors (WC VI)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2x Magmotors (NPC Charity Open-2009 Collegiate Championship)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4x AmpFlow motors (2x per half)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4x Brushed motors</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pittman DC brushed motors (Comedy Central)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Various Ranglebox motors</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2x Castle 2028 brushless motors</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>4x Ampflow E30-400 brushed motors (WC IV)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="G55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2x AmpFlow 48V motors</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2x Ampflow A40-300 motors</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2x NPC T64 motors</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2x TP5680 Brushless inrunner motors</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3x Maytech 6396 brushless motors</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>4x Flipsky 6384 brushless motors</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>T-MOTOR P80III KV100 motors</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2x 80mm brushless outrunner motors (WC V-Present) 2x Sk3-6374 motors (WC I-WC III)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="G63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4x HyperDrive motors (WC VII-Present) 2x NPC-T74 motors (WC III-BB: Champions I)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4x TD6374 Motors</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2x 528-150 Magmotors</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2x Ampflow A28-400 motors</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2x Custom motors</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2x Electric scooter motors</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2x MC160 motors</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2x S28-400 Motors (WC V-BB: Champions I) 2x Neumotors (WC VII-BB: Champions II) 4x Castle brushless motors (BB Proving Ground-Present)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2x Short Magmotors</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2x Surpass 70120 brushless motors</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3x Flipsky 6384 190Kv motors (Drive) 3x unnamed 360Kv motors (Steering)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>3x Maytech brushless motors</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>4x 6474 Brushless motors</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>4x AmpFlow E30-400 motors</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4x AmpFlow F30-150 brushed motors</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4x Ampflow A28-150G brushed motors</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>4x Ampflow A28-400 brushed motors [ 1 ] [ 2 ]</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>4x Bosch GPA-750 motors (Season 4.0) 4x Dustin Motors (Season 5.0)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4x NPC brushed motors</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ampflow A28-150 motor (Rear leg</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>WC I-WC II) Castle brushless motors (BB Proving Ground)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>WC I-WC II) Motenergy ME0909 motor (Vertical spinner</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2x AmpFlow A28-400-F48 motors</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2x Ampflow A28-150 motors</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2x Ampflow brushed motors</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2x Ampflow motors</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2x Bosch GPA-24-750 motors</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4x SK3 motors</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Drive_Type</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Etek motors</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Lifter + Vertical Disk Spinner</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="G93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Articulated Lifter</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vertical Disc Spinner</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="G95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Launcher</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Egg Beater Spinner</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Hammer Saw</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Crusher</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Horizontal Drum Spinner</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Puncher</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Bar spinner (vertical)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>7</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sword</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="G103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Bar spinner (horizontal)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>15</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.428</v>
+      </c>
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Articulated Drum Spinner</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Beater</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Drum Spinner</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Grappler Saw</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Rotary Flipper</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.318</v>
+      </c>
+      <c r="G109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Disc spinner (vertical)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>15</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="G110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Full Body Spinner</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.249</v>
+      </c>
+      <c r="G111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Modular</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="G112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Flipper</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="G113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Drum spinner</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>10</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.069</v>
+      </c>
+      <c r="G114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Disc spinner (horizontal)</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>7</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.057</v>
+      </c>
+      <c r="G115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Horizontal Disc combo</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Swiss Army Bot- flipper</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vertical Drum</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>horizontal spinner</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>kitchen sink</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>vertical spinner</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.054</v>
+      </c>
+      <c r="G122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Fowl Language</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="G123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Kinetic Ring Spinning Flipper</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pneumatic hammer</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Undercutter + Lifter</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>flamethrower</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>launcher</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>vertical bar spinner</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="G129" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>6</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Power Hammer</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="G131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Grappler + Torch</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="G132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Grappler</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>7</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lifter</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>10</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="G134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Axe</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Horizontal Hammersaw</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="G136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Kinetic Krusher</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Full Bodied Spinner</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="G138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Full Bodied Drum Spinner</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="G139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ring Spinner</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="G140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Fire Attack Piercer</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Multibot</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Multiple Weapons</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Poker</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Shooter</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Teeth (Spinning)</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Thwackbot</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Weapon_Type</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Articulated Bar Spinner (vertical)</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
